--- a/resultados/saomateusdosul/inventario_externos.xlsx
+++ b/resultados/saomateusdosul/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8012,6 +8012,4031 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://www.planalto.gov.br/ccivil_03/_Ato2019-2022/2019/Lei/L2931.htm</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>LEI Nº 2.931, DE 30 DE OUTUBRO DE 2019</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/leis_decretos/17126/</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>4</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:41:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.planalto.gov.br/ccivil_03/_Ato2019-2022/2019/Lei/L2883.htm</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>LEI Nº  2.883/2019</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/leis_decretos/17125/</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>4</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1QI-5ZslI2nixRPQVCAgNqS5lNgzZS9ru3m_egwHg1G8/viewform</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1QI-5ZslI2nixRPQVCAgNqS5lNgzZS9ru3m_egwHg1G8/viewform</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2275/comeca-hoje-a-1-conferencia-municipal-da-cidade-de-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>4</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:17:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>http://congresso.redecidadedigital.com.br/</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>congresso.redecidadedigital.com.br</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>aqui</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2276/cidades-digitais-sao-mateus-do-sul-e-representada-na-rodada-de-curitiba-do-i-congresso-paranaense/</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>4</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:17:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://forms.office.com/r/2gEYcvEF6u?origin=lprLink</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>forms.office.com</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>https://forms.office.com/r/2gEYcvEF6u?origin=lprLink</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3329/sao-mateus-do-sul-recebe-palestra-com-jardel-beck-a-cidade-que-queremos-comeca-com-a-nossa-atitude</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>4</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:17:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSe51xiKkvCeIoQzd4C6Zx6ME53o-6o_PpVSzlsRvZWgW9omgw/viewform</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSe51xiKkvCeIoQzd4C6Zx6ME53o-6o_PpVSzlsRvZWgW9omgw/viewform</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3226/sao-mateus-do-sul-promove-curso-gratuito-de-formacao-em-empreendedorismo-feminino</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>4</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:17:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1sdoHsnSBw_g10vAgbp95qIuOTfUXhpAuYI3iIFhWfUg/prefill</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfFBpARsSRMuvZj9AN_CDvN57StsmczsG36GvUN7UrEE9BW4A/viewform</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3128/participe-da-construcao-cultural-de-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>4</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:17:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://l.facebook.com/l.php?u=https%3A%2F%2Fwww.youtube.com%2Fchannel%2FUCxLc-Mxw-OR6XdURRAmXsfQ%3Ffbclid%3DIwAR0Sx6dnP1PHQXT3gMvKs0VtytObvtkRIFrYPQFZXFkEPHghSBKYHAWwN3c&amp;h=AT358jjIWTfecjLl_a9q0571ZR8G08fQlBmawQg7d1jt3qrJo6Ha9kSuDRSplhlKOmfP1dHAwZCxcUIvE8KngjDKtr53q4g2FUpKZbyJvoLJcSVP_bW3Y6pYavT7Lp4joJim&amp;__tn__=-UK*F&amp;c[0]=AT0_rViVldTvpdcunMkwb_xNK_5r5gY2p_aj-9uALAz3hPMTxkcSGl2GiivdzLtVKaInH5RW6pKjYv4Ix30WsDUjkVlu4K14obeLPBRlvZ5X_BEcYnSHIYxDpQfe7F-fX0ZdepjYflg1-U77Sa5YJIh8Tpqa2X6rPPihrytiadV9l3v5MQRR3IlbZAcpoQE_G92w0G_3</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>l.facebook.com</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCxLc-Mxw-OR6XdURRAmXsfQ</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2702/conferencia-municipal/</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>4</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://l.facebook.com/l.php?u=https%3A%2F%2Fdocs.google.com%2Fforms%2Fd%2Fe%2F1FAIpQLSe4vZ7ZDP3fYdXVbYHi__XqCA-zEFUS8d7qfkQndXIX_xFzQg%2Fviewform%3Ffbclid%3DIwAR3qAwKLXKeeQuGHsDB3XVtibqxghsLJ5TeD2QL_2tVXFe_HnQ8LQTA4PZw&amp;h=AT1L8_sVyR-Jn6Gyiq2Ing7XX4mLkW3wW4Xn_0Z7RhC872bgrrVS2XloDmz215gF9oH_SOGHmSHDkEbRpQTjp5ZMic7VDwPN3kSHvSeCeAhgyx1hl4cVIQrOKNp0p1Z22rnz&amp;__tn__=-UK*F&amp;c[0]=AT0_rViVldTvpdcunMkwb_xNK_5r5gY2p_aj-9uALAz3hPMTxkcSGl2GiivdzLtVKaInH5RW6pKjYv4Ix30WsDUjkVlu4K14obeLPBRlvZ5X_BEcYnSHIYxDpQfe7F-fX0ZdepjYflg1-U77Sa5YJIh8Tpqa2X6rPPihrytiadV9l3v5MQRR3IlbZAcpoQE_G92w0G_3</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>l.facebook.com</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/.../1FAIpQLSe4vZ7ZDP3fYd.../viewform</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2702/conferencia-municipal/</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>4</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://l.facebook.com/l.php?u=https%3A%2F%2Fwww.youtube.com%2Fchannel%2FUCxLc-Mxw-OR6XdURRAmXsfQ%3Ffbclid%3DIwAR2kxgWEMupE15UFHOdGKZbfPdQ3gJiPIQI4h-2YI0RBWbQU8RSLvqoXnS0&amp;h=AT358jjIWTfecjLl_a9q0571ZR8G08fQlBmawQg7d1jt3qrJo6Ha9kSuDRSplhlKOmfP1dHAwZCxcUIvE8KngjDKtr53q4g2FUpKZbyJvoLJcSVP_bW3Y6pYavT7Lp4joJim&amp;__tn__=-UK*F&amp;c[0]=AT0_rViVldTvpdcunMkwb_xNK_5r5gY2p_aj-9uALAz3hPMTxkcSGl2GiivdzLtVKaInH5RW6pKjYv4Ix30WsDUjkVlu4K14obeLPBRlvZ5X_BEcYnSHIYxDpQfe7F-fX0ZdepjYflg1-U77Sa5YJIh8Tpqa2X6rPPihrytiadV9l3v5MQRR3IlbZAcpoQE_G92w0G_3</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>l.facebook.com</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCxLc-Mxw-OR6XdURRAmXsfQ</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2702/conferencia-municipal/</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>4</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://l.facebook.com/l.php?u=https%3A%2F%2Fwww.youtube.com%2Fwatch%3Fv%3D3GPLxeOvKmg%26fbclid%3DIwAR0JSQmdtuw1SQEOQeqqTNqo7sIRaHNYo1_WY0B4E_YVGCkKW4_EksLKFSo&amp;h=AT1BTFseJ7zluLrgPx-buEvGc30MxTiocjQ-RJEU_jD0w6E8TYsgYW8DL0PhxxbTRm2IwvfvL8joDjCFgtneDyzSFLZFuSe-97gw7tnkotpU1Ac2FKrdidjCaq1GNgCn5wv2&amp;__tn__=-UK-R&amp;c[0]=AT2MyvDa23c0nKMCWuvrl5SQcDbI8CEXoUMYoYSObku-e4uF9IMqHVLeOKknrqBcy3OQYAzo01LA-M6pHb1BTq-vx2BV4j41jdwDoEyOFrqZIc7AqAIIHya733lua3mzeuyRI7kZC_O3x8jf7ajxOlyyE2kuL5ojNYnansE3nTQj9dv-hnK_0MahYepJF7h8AN9S4CB31D0Jtta41bo4iFI</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>l.facebook.com</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQ47Taqrud0</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2685/conferencia-de-assistencia-social-e-amanha/</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>4</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hqEe2tJXwhfedGaQ7?fbclid=IwAR0_GYx9E5-sBGeRbCTHejpQzQd1ZeqlYRnTyCQJquaza23yDIslWDPPabU</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hqEe2tJXwhfedGaQ7</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2685/conferencia-de-assistencia-social-e-amanha/</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>4</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hqEe2tJXwhfedGaQ7</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>https://forms.gle/hqEe2tJXwhfedGaQ7</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2675/sao-mateus-do-sul-promovera-xii-conferencia-de-assistencia-social/</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>4</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://forms.gle/PewmwjkDqq7bSgnm7</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>https://forms.gle/PewmwjkDqq7bSgnm7</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2997/mathelab-inscricoes-estao-abertas-para-workshop-sobre-erva-mate/</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>4</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://www.agricultura.pr.gov.br/servicos/Agropecuaria/Pecuaria/Emitir-guia-de-transito-animal-GTA-GPoyMBoQ</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>www.agricultura.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Guia de Trânsito Animal (GTA)</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2911/produtores-tem-ate-30-de-junho-para-fazer-atualizacao-cadastral-de-rebanhos/</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>4</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://www.adapar.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>www.adapar.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>pelo site</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2911/produtores-tem-ate-30-de-junho-para-fazer-atualizacao-cadastral-de-rebanhos/</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>4</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>http://www.adapar.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>www.adapar.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>da Adapar</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2911/produtores-tem-ate-30-de-junho-para-fazer-atualizacao-cadastral-de-rebanhos/</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>4</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=br.gov.pr.celepar.seab.paranaagro&amp;hl=pt_BR&amp;gl=US&amp;pli=1</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>play.google.com</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>aplicativo Paraná Agro</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2911/produtores-tem-ate-30-de-junho-para-fazer-atualizacao-cadastral-de-rebanhos/</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>4</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>http://www.produtor.adapar.pr.gov.br/login</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>www.produtor.adapar.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>deste link</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2911/produtores-tem-ate-30-de-junho-para-fazer-atualizacao-cadastral-de-rebanhos/</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>4</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>http://Relações Públicas</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Relações Públicas</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Adapar</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2911/produtores-tem-ate-30-de-junho-para-fazer-atualizacao-cadastral-de-rebanhos/</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>4</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://www.aen.pr.gov.br/Noticia/Confaz-prorroga-para-2024-adesao-obrigatoria-da-Nota-Fiscal-Eletronica-do-Produtor-Rural</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Aen</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2909/confaz-prorroga-para-2024-adesao-obrigatoria-da-nota-fiscal-eletronica-do-produtor-rural/</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>4</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:21:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/con_comprasdiretascovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Compras diretas referente a Covid-19</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/enfrentamento-ao-coronavirus</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>4</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/con_contratoscovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Contratos referente a Covid-19</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/enfrentamento-ao-coronavirus</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>4</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/con_despesasempenhadascovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Empenhos referente a Covid-19</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/enfrentamento-ao-coronavirus</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>4</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/con_licitacoescovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Licitações referente a Covid-19</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/enfrentamento-ao-coronavirus</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>4</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/con_receitascovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Receitas referente a Covid-19</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/enfrentamento-ao-coronavirus</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>4</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/CCIVIL_03/Portaria/quadro_portaria.htm</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LEGISLAÇÃO FEDERAL</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/legislacao</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>4</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>http://www.coronavirus.pr.gov.br/Campanha/Pagina/TRANSPARENCIA-Enfrentamento-ao-Coronavirus-3</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>www.coronavirus.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>LEGISLAÇÃO ESTADUAL</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/legislacao</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>4</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/01037-059/con_receitascovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>- RECEITAS</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/execucao-orcamentaria</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>4</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/01037-059/con_despesasempenhadascovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>- DESPESAS</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/execucao-orcamentaria</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>4</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>http://e-gov.betha.com.br/transparencia/01037-059/con_receitaversusdespesacovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>- RELATÓRIO COVID-19:RECEITAS X DESPESAS</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/execucao-orcamentaria</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>4</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/01037-063/con_relatorios_opcionais_link17.faces</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/execucao-orcamentaria</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>4</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/01037-062/con_licitacoescovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DISPENSAS DE LICITAÇÕES</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/licitacoes</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>4</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/01037-059/con_comprasdiretascovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>COMPRAS DIRETAS</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/licitacoes</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>4</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/transparencia/01037-059/con_contratoscovid.faces?mun=BFajgIVxrBs=</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CONTRATOS</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/licitacoes</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>4</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.objetivas.com.br/arquivos/2019/10/JZhyTXsHjZ_edital.pdf</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>www.objetivas.com.br</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>https://www.objetivas.com.br/arquivos/2019/10/JZhyTXsHjZ_edital.pdf</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>4</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:42:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_Ato2007-2010/2009/Lei/L11947.htm</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Lei nº 13 987, de 07 de abril de 2009</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>4</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-n-2-de-9-de-abril-de-2020-252085843</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>www.in.gov.br</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Resolução n° 02, de 09 de abril de 2020</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>4</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>http://www.cee.pr.gov.br/arquivos/File/pdf/Deliberacoes/2020/deliberacao_01_20.pdf</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>www.cee.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>http://www.cee.pr.gov.br/arquivos/File/pdf/Deliberacoes/2020/deliberacao_01_20.pdf</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>4</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://forms.gle/fZXNDf3ziQzSfD7XA</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>forms.gle</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>https://forms.gle/fZXNDf3ziQzSfD7XA</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>4</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://integrafaculdades.com.br</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>integrafaculdades.com.br</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>https://integrafaculdades.com.br</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>4</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://vivescer.org.br/cadastro/</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>vivescer.org.br</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>https://vivescer.org.br/cadastro/</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>4</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2019-2022/2020/lei/l13982.htm</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Lei Nº 13.982</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>4</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>http://https://www.legislacao.pr.gov.br/legislacao/listarAtosAno.do?action=exibir&amp;codAto=233624&amp;codTipoAto=&amp;tipoVisualizacao=original</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https:</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Lei Nº 20.172 de 7 de abril de 2020</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>4</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://www.legislacao.pr.gov.br/legislacao/listarAtosAno.do?action=exibir&amp;codAto=234181&amp;codTipoAto=&amp;tipoVisualizacao=original</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>www.legislacao.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Decreto Nº 4570</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>4</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2019-2022/2020/lei/l13987.htm</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Lei Nº 13.987 de 7 de abril de 2020</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>4</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://www.fonoaudiologia.org.br/cffa/index.php/pareceres-e-recomendacoes/</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>www.fonoaudiologia.org.br</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>https://www.fonoaudiologia.org.br/cffa/index.php/pareceres-e-recomendacoes/</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>4</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://www.crefito8.gov.br/pr/index.php/ultimas-noticias/2405-covid-19-atendimentos-de-terapia-ocupacional-no-estado-d-parana-2</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>www.crefito8.gov.br</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>https://www.crefito8.gov.br/pr/index.php/ultimas-noticias/2405-covid-19-atendimentos-de-terapia-ocupacional-no-estado-d-parana-2</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>4</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://www.coffito.gov.br/nsite/?p=15825</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>www.coffito.gov.br</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>https://www.coffito.gov.br/nsite/?p=15825</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>4</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>http://saomateusdosul.apaepr.org.br/pagina/programa-nacional-de-apoio-a-atencao-da-saude-da-pessoa-com-deficiencia-pronaspcd</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>saomateusdosul.apaepr.org.br</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>http://saomateusdosul.apaepr.org.br/pagina/programa-nacional-de-apoio-a-atencao-da-saude-da-pessoa-com-deficiencia-pronaspcd</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>4</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>http://saomateusdosul.apaepr.org.br/pagina/programa-nacional-de-apoio-a-atencao-da-saude-da-pessoa-com-deficiencia-pronaspcd) (http://www.planalto.gov.br/ccivil_03/_ato2011-2014/2012/lei/l12715.htm</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>saomateusdosul.apaepr.org.br</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>) (</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>4</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2011-2014/2012/lei/l12715.htm</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2011-2014/2012/lei/l12715.htm</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>4</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://undime.org.br/uploads/documentos/php7us6wi_5ef60b2c141df.pdf</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>undime.org.br</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>https://undime.org.br/uploads/documentos/php7us6wi_5ef60b2c141df.pdf</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>4</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>http://www.consed.org.br/portal/noticia/consed-lanca-diretrizes-para-protocolos-de-retorno-as-aulas</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>www.consed.org.br</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>http://www.consed.org.br/portal/noticia/consed-lanca-diretrizes-para-protocolos-de-retorno-as-aulas</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>4</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://static.poder360.com.br/2020/05/todos-pela-educacao.pdf</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>static.poder360.com.br</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>https://static.poder360.com.br/2020/05/todos-pela-educacao.pdf</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>4</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://www.tribunapr.com.br/noticias/parana/secretaria-da-educacao-apresenta-plano-para-volta-as-aulas-no-parana-veja-detalhes/</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>www.tribunapr.com.br</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>www.tribunapr.com.br/noticias/parana/secretaria-da-educacao-apresenta-plano-para-volta-as-aulas-no-parana-veja-detalhes</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>4</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://undime.org.br/noticia/22-06-2020-17-54-undime-divulga-documento-com-subsidios-para-a-elaboracao-de-protocolos-de-retorno-as-aulas-presenciais</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>undime.org.br</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>https://undime.org.br/noticia/22-06-2020-17-54-undime-divulga-documento-com-subsidios-para-a-elaboracao-de-protocolos-de-retorno-as-aulas-presenciais</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>4</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://www.todospelaeducacao.org.br/_uploads/_posts/433.pdf?1194110764</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>www.todospelaeducacao.org.br</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>https://www.todospelaeducacao.org.br/_uploads/_posts/433.pdf?1194110764</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/educacao</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>4</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://servicos.tce.pr.gov.br/TCEPR/Tribunal/Relacon</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>servicos.tce.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>TCEPR</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/obras</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>4</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>http://www.tce.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>www.tce.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Tribunal de Contas do Estado do Paraná</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/obras</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>4</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://www.planalto.gov.br/ccivil_03/Decreto-Lei/Del5452.htm</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Atender  o Art. 456-A. Cabe ao empregador definir o padrão de vestimenta no meio ambiente laboral, sendo lícita a inclusão no uniforme de logomarcas da própria empresa ou de empresas parceiras e de outros itens de identificação relacionados à atividade desempenhada.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/plano-de-contratacao-anual-2025</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>4</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>http://www.coronavirus.pr.gov.br/Campanha/FAQ/Tire-suas-duvidas-Acoes-do-Governo-do-Parana</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>www.coronavirus.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Veja quais as medidas já adotadas pelo Governo do Estado do Paraná para o Combate ao novo Coronavírus no Estado</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/coronavirus</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>4</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>http://www.coronavirus.pr.gov.br/Campanha</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>www.coronavirus.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Acompanhe as últimas notícias direto do portal do governo do Paraná</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/coronavirus</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>4</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:43:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/explore/tags/aportederecursos/</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>#AporteDeRecursos</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3099/aporte-de-recursos-para-saude-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>5</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:48:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/explore/tags/sa%C3%BAdeparatodos/</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>#SaúdeParaTodos</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3099/aporte-de-recursos-para-saude-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>5</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:48:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/explore/tags/s%C3%A3omateusdosul/</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>#SãoMateusDoSul</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3099/aporte-de-recursos-para-saude-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>5</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:48:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>http://www.produtor.adapar.pr.gov.br/comprovacaorebanho</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>www.produtor.adapar.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>http://www.produtor.adapar.pr.gov.br/comprovacaorebanho</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2456/campanha-de-atualizacao-do-rebanho-2019</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>5</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:49:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/prefeiturasms?__eep__=6&amp;__cft__[0]=AZXfTHFOsJcpJ4ixmod25tKaQVOsoJNKqS8wRHxlSeNS-IGw3UhY1m-_cc5kpdmACs2ijDo3DXWTtSndARPgp4Zd7nHaB5cowwuu-xsQAheBrv5mFvZqXIhaNnJMHpx_IkGGdWRhF3LUSeHK5z-hJIQSFL-_RzYIpmkzhywp3Ge8-bI5w3auWUhyAdUylsNs9TtJruXquE-lj5yj517-am9l&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>#prefeiturasms</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2842/programa-castrapet-inicia-castracoes-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>5</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/meioambiente?__eep__=6&amp;__cft__[0]=AZXfTHFOsJcpJ4ixmod25tKaQVOsoJNKqS8wRHxlSeNS-IGw3UhY1m-_cc5kpdmACs2ijDo3DXWTtSndARPgp4Zd7nHaB5cowwuu-xsQAheBrv5mFvZqXIhaNnJMHpx_IkGGdWRhF3LUSeHK5z-hJIQSFL-_RzYIpmkzhywp3Ge8-bI5w3auWUhyAdUylsNs9TtJruXquE-lj5yj517-am9l&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>#meioambiente</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2842/programa-castrapet-inicia-castracoes-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>5</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/articulacaonacionaldeagroecologia/?__cft__[0]=AZXadxNHKYHNZ94TRzr4b5P9ByeUgLQlUs7cXg3KtUCCupjGH9bvXNxi_PUhj00y8FPeUSbSN99McxOR7LOVuUhsN-KT5tGK19Wh0Rm5xqCfsX1iFsoXMFeVQL8Ak--KmJPSN8CZhqP2g589N5kWub1Zysmc1KZfmNeBAa6QVzCg8xfMfdlfJFUcSL7M7EFHZAk&amp;__tn__=kK-R</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Articulação Nacional de Agroecologia (ANA)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2686/projeto-sao-mateus-do-sul-agroecologico/</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>5</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/agroecologianosmunic%C3%ADpios?__eep__=6&amp;__cft__[0]=AZXadxNHKYHNZ94TRzr4b5P9ByeUgLQlUs7cXg3KtUCCupjGH9bvXNxi_PUhj00y8FPeUSbSN99McxOR7LOVuUhsN-KT5tGK19Wh0Rm5xqCfsX1iFsoXMFeVQL8Ak--KmJPSN8CZhqP2g589N5kWub1Zysmc1KZfmNeBAa6QVzCg8xfMfdlfJFUcSL7M7EFHZAk&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>#AgroecologiaNosMunicípios</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2686/projeto-sao-mateus-do-sul-agroecologico/</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>5</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/agroecologia?__eep__=6&amp;__cft__[0]=AZXadxNHKYHNZ94TRzr4b5P9ByeUgLQlUs7cXg3KtUCCupjGH9bvXNxi_PUhj00y8FPeUSbSN99McxOR7LOVuUhsN-KT5tGK19Wh0Rm5xqCfsX1iFsoXMFeVQL8Ak--KmJPSN8CZhqP2g589N5kWub1Zysmc1KZfmNeBAa6QVzCg8xfMfdlfJFUcSL7M7EFHZAk&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>#Agroecologia</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2686/projeto-sao-mateus-do-sul-agroecologico/</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>5</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/pol%C3%ADticasdefuturo?__eep__=6&amp;__cft__[0]=AZXadxNHKYHNZ94TRzr4b5P9ByeUgLQlUs7cXg3KtUCCupjGH9bvXNxi_PUhj00y8FPeUSbSN99McxOR7LOVuUhsN-KT5tGK19Wh0Rm5xqCfsX1iFsoXMFeVQL8Ak--KmJPSN8CZhqP2g589N5kWub1Zysmc1KZfmNeBAa6QVzCg8xfMfdlfJFUcSL7M7EFHZAk&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>#PolíticasDeFuturo</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2686/projeto-sao-mateus-do-sul-agroecologico/</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>5</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/planomunicipaldeagroecologia?__eep__=6&amp;__cft__[0]=AZXadxNHKYHNZ94TRzr4b5P9ByeUgLQlUs7cXg3KtUCCupjGH9bvXNxi_PUhj00y8FPeUSbSN99McxOR7LOVuUhsN-KT5tGK19Wh0Rm5xqCfsX1iFsoXMFeVQL8Ak--KmJPSN8CZhqP2g589N5kWub1Zysmc1KZfmNeBAa6QVzCg8xfMfdlfJFUcSL7M7EFHZAk&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>#PlanoMunicipalDeAgroecologia</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2686/projeto-sao-mateus-do-sul-agroecologico/</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>5</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/pol%C3%ADticasp%C3%BAblicas?__eep__=6&amp;__cft__[0]=AZXadxNHKYHNZ94TRzr4b5P9ByeUgLQlUs7cXg3KtUCCupjGH9bvXNxi_PUhj00y8FPeUSbSN99McxOR7LOVuUhsN-KT5tGK19Wh0Rm5xqCfsX1iFsoXMFeVQL8Ak--KmJPSN8CZhqP2g589N5kWub1Zysmc1KZfmNeBAa6QVzCg8xfMfdlfJFUcSL7M7EFHZAk&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>#PolíticasPúblicas</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2686/projeto-sao-mateus-do-sul-agroecologico/</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>5</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:50:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZVHafyGUgtIgQJ4Mrf7E5jkKtuK0AyQIwwSyHoEHDsLl_AOiaihAw_g3PtnuEFwhpVZl0-_wteCDnOM2vxjmAl6Eho5OTU1twJZE598KIR29IrMEpNWUHLnucx3Iz32n_P9T9a3FUNVF-kfhxrAx1xi4xWPO_mYhsnefx5iqCfOXg4aexKNWXzKUb4edE7lXkQ&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2665/vacinacao-36-anos-ou-mais</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>5</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:53:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__cft__[0]=AZVHafyGUgtIgQJ4Mrf7E5jkKtuK0AyQIwwSyHoEHDsLl_AOiaihAw_g3PtnuEFwhpVZl0-_wteCDnOM2vxjmAl6Eho5OTU1twJZE598KIR29IrMEpNWUHLnucx3Iz32n_P9T9a3FUNVF-kfhxrAx1xi4xWPO_mYhsnefx5iqCfOXg4aexKNWXzKUb4edE7lXkQ&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>#VacinaSama</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2665/vacinacao-36-anos-ou-mais</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>5</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:53:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZXRtNVpqmbuapkhtCCdVYLNsalEfASoCOeXKsQLuErtMsROSpS_I0nQcGYWEb-BWeplZNCmTGS5rU7Fa-zqs1ljW-AgdHtbpGGRUJLrcRlMOUnuxFZ4vxnIID7e0Rnu66zErJhlMBtIIQvQsVGP9ixdhZyRkvNkn0knoYya3oqKm8whvyUKRNkrGS2-ivqKdFM&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2661/vacinacao-37-anos-ou-mais</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>5</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:53:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__cft__[0]=AZXRtNVpqmbuapkhtCCdVYLNsalEfASoCOeXKsQLuErtMsROSpS_I0nQcGYWEb-BWeplZNCmTGS5rU7Fa-zqs1ljW-AgdHtbpGGRUJLrcRlMOUnuxFZ4vxnIID7e0Rnu66zErJhlMBtIIQvQsVGP9ixdhZyRkvNkn0knoYya3oqKm8whvyUKRNkrGS2-ivqKdFM&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>#VacinaSamas</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2661/vacinacao-37-anos-ou-mais</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>5</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:53:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://www.municipios.sigo.pr.gov.br/cidadao/8</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>www.municipios.sigo.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>https://www.municipios.sigo.pr.gov.br/cidadao/8</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2805/comunicado/</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>5</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:53:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://www.maletamagica.com.br/</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>www.maletamagica.com.br</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>https://www.maletamagica.com.br/</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2814/exposicao-em-sao-mateus-do-sul-pr-permite-conhecer-o-cinema-de-animacao-e-produzir-filmes-participativos</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>5</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/expo.maletamagica</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/expo.maletamagica</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2814/exposicao-em-sao-mateus-do-sul-pr-permite-conhecer-o-cinema-de-animacao-e-produzir-filmes-participativos</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>5</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/expo.maletamagica/</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/expo.maletamagica/</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2814/exposicao-em-sao-mateus-do-sul-pr-permite-conhecer-o-cinema-de-animacao-e-produzir-filmes-participativos</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>5</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/maiseducacao?__eep__=6&amp;__cft__[0]=AZU9W3-ExkA8_HLcVY7n5smyN27dgwYT6jAX7eYuWWwXKfzmr4iyocfxTDBGc8t-AfGvpszs2knpqns7tAPQoLvH6E40ywAD5LkJOtGQHbH1BqcZD7Ysq_RLrIgXMAqbJSkfD8PFNXZe213EGYtygv0Xl_0FEa8cRkrRBmyjdOizdfjDn5UnTbL408ewcuEVqOQ&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>#maiseducacao</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2810/secretaria-de-educacao-faz-acao-itinerante-em-atendimento-as-rematriculas-nos-cmeis</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>5</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:54:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/prefeiturasms?__eep__=6&amp;__cft__[0]=AZU9W3-ExkA8_HLcVY7n5smyN27dgwYT6jAX7eYuWWwXKfzmr4iyocfxTDBGc8t-AfGvpszs2knpqns7tAPQoLvH6E40ywAD5LkJOtGQHbH1BqcZD7Ysq_RLrIgXMAqbJSkfD8PFNXZe213EGYtygv0Xl_0FEa8cRkrRBmyjdOizdfjDn5UnTbL408ewcuEVqOQ&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>#prefeiturasms</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2810/secretaria-de-educacao-faz-acao-itinerante-em-atendimento-as-rematriculas-nos-cmeis</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>5</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:54:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/natalouroverde?__eep__=6&amp;__cft__[0]=AZVKaigz6C27xE37SGaSpeifx4TEwU2tGJUHTE-7XlAUr8xm5-1m-wxo9ZyakjFYBo1_369-Rdctwz8SpgHmx_R0yIaNF7jcdrHyrr06vlkgvE3SceKKkxtG8rVcWys0QLLP88DnB51U8Qd2QRcgKH-HohkKqy5N3ErtIXyGO1P-6XF63V2oXvUxHjVI9Djp5lc&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>#natalouroverde</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2725/marque-na-agenda</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>5</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/emfamilia?__eep__=6&amp;__cft__[0]=AZVKaigz6C27xE37SGaSpeifx4TEwU2tGJUHTE-7XlAUr8xm5-1m-wxo9ZyakjFYBo1_369-Rdctwz8SpgHmx_R0yIaNF7jcdrHyrr06vlkgvE3SceKKkxtG8rVcWys0QLLP88DnB51U8Qd2QRcgKH-HohkKqy5N3ErtIXyGO1P-6XF63V2oXvUxHjVI9Djp5lc&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>#emfamilia</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2725/marque-na-agenda</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>5</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/natalouroverde?__eep__=6&amp;__cft__[0]=AZXtfWgOHMo31XPc9Brzvn4I4VcIaV8rKfmSx-u63adkLwGTWG2WYTQ5MDav1lJ0-9rwYm9z5SS6GdOEoc--2JY84xEVvXvOW816dW6XDJF5KdMGOxgeYxcgLoVnaXJ_y9cXjKJdc4tbkaZWvogcNtnWCxHB_n4LePuJrULdg1WRg7IHhOwDUaNzCdguIW_OAmw&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>#natalouroverde</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2725/marque-na-agenda</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>5</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/emfamilia?__eep__=6&amp;__cft__[0]=AZXtfWgOHMo31XPc9Brzvn4I4VcIaV8rKfmSx-u63adkLwGTWG2WYTQ5MDav1lJ0-9rwYm9z5SS6GdOEoc--2JY84xEVvXvOW816dW6XDJF5KdMGOxgeYxcgLoVnaXJ_y9cXjKJdc4tbkaZWvogcNtnWCxHB_n4LePuJrULdg1WRg7IHhOwDUaNzCdguIW_OAmw&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>#emfamilia</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2725/marque-na-agenda</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>5</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-08-07 12:55:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xHkvJtUrCDA</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>veja aqui</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2897/jenifer-jaworsk-e-eleita-miss-parana-2023-e-traz-a-coroa-para-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>5</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://inscricoes.apps.uepg.br/</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>inscricoes.apps.uepg.br</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>https://inscricoes.apps.uepg.br/</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2698/lei-aldir-blanc---sao-mateus-do-sul-possui-49-vagas-para-programa-de-bolsas/</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>5</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:21:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://www.nucleoasdepaus.com.br/pereira-da-tia-miseria/</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>www.nucleoasdepaus.com.br</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>A Pereira da Tia Miséria</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2453/a-peca/</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>5</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:21:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://ciaradicalidade.wordpress.com/</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>ciaradicalidade.wordpress.com</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>https://ciaradicalidade.wordpress.com</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2445/sao-mateus-do-sul-apresenta-a-peca/</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>5</v>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:21:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://sistemas.uepg.br/lato</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sistemas.uepg.br</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>https://sistemas.uepg.br/lato</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2023/uab-oferece-especializacao-em-gestao-educacional/</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>5</v>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>http://www.nutead.org/site/index.php/nutead/confira-os-cursos-de-especializacao-com-inscricoes-abertas/</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>www.nutead.org</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>http://www.nutead.org/site/index.php/nutead/confira-os-cursos-de-especializacao-com-inscricoes-abertas/</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2023/uab-oferece-especializacao-em-gestao-educacional/</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>5</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/polouabsaomateusdosul</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>www.facebook.com/polouabsaomateusdosul</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2033/selecao-para-vagas-para-4-edicao-de-curso-de-especializacao-em-gestao-educacional-organizacao-escolar-e-trabalho-pedagogico/</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>5</v>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>http://www.planalto.gov.br/ccivil_03/_ato2007-2010/2007/Lei/L11494.htm</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LEI Nº 11.494, DE 20 DE JUNHO DE 2007</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2278/reuniao-marca-inicio-de-atividades-da-comissao-do-fundeb/</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>5</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/08/ficha-de-inscricao-campeonato-smetur-de-futsal-2019.docx</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>FICHA DE INSCRIÇÃO CAMPEONATO DE FUTSAL 2019</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2429/estao-abertas-as-inscricoes-para-o-campeonato-municipal-de-futsal-2019/</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>5</v>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/08/autorizacao-campeonato-de-futsal-2019.docx</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>AUTORIZAÇÃO CAMPEONATO MUNICIPAL DE FUTSAL 2019</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2429/estao-abertas-as-inscricoes-para-o-campeonato-municipal-de-futsal-2019/</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>5</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/08/regulamento-campeonato-municipal-de-futsal-2019-2.pdf</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Regulamento Campeonato Municipal de Futsal 2019</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2429/estao-abertas-as-inscricoes-para-o-campeonato-municipal-de-futsal-2019/</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>5</v>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/resultados.pdf</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Resultados Fases de Grupos;</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1078/equipes-sao-mateuenses-se-destacam-e-passam-para-a-proxima-fase-dos-32-jogos-da-juventude-do-parana-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>5</v>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/programacao-2.pdf</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Programação Segunda Fase do 32º JOJUPS.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1078/equipes-sao-mateuenses-se-destacam-e-passam-para-a-proxima-fase-dos-32-jogos-da-juventude-do-parana-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>5</v>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/programacao.pdf</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Programação JOJUPS - São Mateus do Sul.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1083/cerimonia-de-abertura-dos-jogos-da-juventude-do-parana-lota-ginasio-olivio-wolff-do-amaral/</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>5</v>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/rodada-02.pdf</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>RODADA 02</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1109/acontece-neste-final-de-semana-a-2-rodada-do-campeonato-municipal-de-futebol-promovida-pela-secretaria-de-esportes/</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>5</v>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/resultado-rodada-01.pdf</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>RESULTADO - RODADA 01</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1109/acontece-neste-final-de-semana-a-2-rodada-do-campeonato-municipal-de-futebol-promovida-pela-secretaria-de-esportes/</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>5</v>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/boletim-oficial-n°-_-03-66-jeps-alterado-tranporte-semec.pdf</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>BOLETIM OFICIAL 66º JEPS.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1120/66-fase-municipal-dos-jogos-escolares-do-parana-iniciam-hoje-quarta-feira-5-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>5</v>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/grupamento-jeps-2019.pdf</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>GRUPAMENTO JEPS 2019</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1120/66-fase-municipal-dos-jogos-escolares-do-parana-iniciam-hoje-quarta-feira-5-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>5</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/05/regulamento-campeonato-municipal-de-futebol-2019.pdf</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>REGULAMENTO CAMPEONATO MUNICIPAL DE FUTEBOL 2019</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1130/campeonato-municipal-de-futebol-2019/</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>5</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/05/ficha-de-inscricao-futebol-2019.docx</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>FICHA DE INSCRIÇÃO FUTEBOL 2019</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1130/campeonato-municipal-de-futebol-2019/</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>5</v>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>http://www.fprm.com.br/</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>www.fprm.com.br</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>www.fprm.com.br</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2137/comunicado-da-secretaria-municipal-de-esporte-e-turismo/</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>5</v>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/2019-01-edital-de-abertura-das-inscricoes-1.pdf</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2019-01 - Edital de Abertura das Inscrições (1)</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1117/inscricoes-para-o-concurso-publico-da-prefeitura-de-sao-mateus-do-sul-estao-reabertas</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>5</v>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/2019-01-a-retifica-o-edital-de-abertura-das-inscricoes-e-reabre-o-periodo-de-inscricoes-1-1.pdf</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2019-01-A - Retifica o Edital de Abertura das Inscrições e reabre o período de inscrições (1)</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1117/inscricoes-para-o-concurso-publico-da-prefeitura-de-sao-mateus-do-sul-estao-reabertas</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>5</v>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:23:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://www.objetivas.com.br/arquivos/2019/04/2vby2Gnjhs_edital.pdf</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>www.objetivas.com.br</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>https://www.objetivas.com.br/arquivos/2019/04/2vby2Gnjhs_edital.pdf</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1147/comunicado-oficial-n-012019--concurso-publico</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>5</v>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:24:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/cuidedequemvoceama?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDp7lUJIIAcsTaWTy07APztYO0jEVS3bUsZjo2dFMtpgl8MZpgV59sa8KTQHZiNTeWr79-JUpzt6BmeTHyW0598NhKZE8bTJVpjDa2EBhpdnS4CLAgjvIw74H9_RhCLDr6GHO-Yx2-nKJaS1xsAipN9U9I6if80R1bwCcCJgS5PbqlunHdTiBye8UrlfRGS6LyA0tvIijc-WHMkdZSrVXvHac1KNdm72VFaEZGE576AntW9oEZ2nnRg7LFxlXygcvSYrx_tD9cdu8CTNpQROEU9qTwUGdWr78LoCoGH1KdNYtwN1uSFUxE&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>#CuideDeQuemVoceAma</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2575/vacinacao-para-idosos-de-80-anos</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>5</v>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:24:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>http://www.cps.uepg.br/pss</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>www.cps.uepg.br</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>www.cps.uepg.br/pss</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1822/uepg-anuncia-periodo-de-inscricao-ao-pss-2015</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>5</v>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-08-07 14:24:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saomateusdosul/inventario_externos.xlsx
+++ b/resultados/saomateusdosul/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G333"/>
+  <dimension ref="A1:G458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12037,6 +12037,4365 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://www.planalto.gov.br/ccivil_03/_Ato2019-2022/2019/Lei/L2927.htm</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>LEI N° 2.927, DE 23 DE OUTUBRO DE 2019</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/leis_decretos/17139/</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>5</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-08-07 22:03:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/watch?v=15tFuKLQI7I</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/watch?v=15tFuKLQI7I</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2338/prefeitura-inova-e-transmite-audiencia-publica-pela-internet/</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>5</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>http://eventos.unicentro.br/uab_pnap_aluno/edital_001_2013.pdf</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>eventos.unicentro.br</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>http://eventos.unicentro.br/uab_pnap_aluno/edital_001_2013.pdf</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2345/inscricoes-abertas-para-cursos-de-pos-graduacao/</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>5</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>http://sites.unicentro.br/uab/midiasnaeducacao/editais/</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>sites.unicentro.br</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>http://sites.unicentro.br/uab/midiasnaeducacao/editais/</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2345/inscricoes-abertas-para-cursos-de-pos-graduacao/</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>5</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>http://www.unicentro.br/uab/</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>www.unicentro.br</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>www.unicentro.br/uab/</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2345/inscricoes-abertas-para-cursos-de-pos-graduacao/</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>5</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://play.google.com/store/apps/details?id=br.gov.caixa.fgts.trabalhador&amp;hl=pt_BR&amp;gl=US</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>play.google.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Google Play</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3066/sao-mateuenses-atingidos-por-cheias-podem-realizar-saque-calamidade-do-fgts/</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>5</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://apps.apple.com/br/app/fgts/id1038441027</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>apps.apple.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Apple Store</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3066/sao-mateuenses-atingidos-por-cheias-podem-realizar-saque-calamidade-do-fgts/</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>5</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>http://www.istoe.com.br/reportagens/436873_CURITIBA+E+ELEITA+A+MELHOR+CIDADE+DO+BRASIL+PELO+RANKING+ISTOE+AUSTIN+RATINGS?pathImagens=&amp;path=&amp;actualArea=internalPage</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>www.istoe.com.br</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Curitiba é eleita a melhor cidade do Brasil pelo ranking Istoé/Austin Ratings</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1748/avancos-sociais-colocam-sao-mateus-do-sul-entre-as-20-melhores-cidades-para-se-viver/</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>5</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>http://www.cps.uepg.br/</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>www.cps.uepg.br</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>www.cps.uepg.br</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1810/uepg-divulga-ensalamento-do-vestibular-de-inverno-2015/</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>5</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:11:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/apiariosapiculturabimel</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>@apiariosapiculturabimel</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3300/curso-de-artesanato-com-produtos-das-abelhas-incentiva-o-autocuidado-masculino-e-a-geracao-de-renda-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>5</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:12:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSe1i0GIFhEN_lhuZUmq-Odk-CVM8bj_2xbihcWbtg_6qZf_5g/viewform?fbclid=IwAR1KNbssTMQ7YNyjQEKv4xqItF2MH1RZcO-5amfcLOOKmyH6BgoZ08h2R1s</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSe1i0GIFhEN_lhuZUmq-Odk-CVM8bj_2xbihcWbtg_6qZf_5g/viewform</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2443/palestra-aprenda-a-participar-de-licitacoes-publicas</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>5</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>http://amsulpar.com.br/edital-no-00120013-cidepsul-teste-seletivo-contratacao-de-operadores-de-maquinas-e-motoristas-de-caminhao-basculante/</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>amsulpar.com.br</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>http://amsulpar.com.br/edital-no-00120013-cidepsul-teste-seletivo-contratacao-de-operadores-de-maquinas-e-motoristas-de-caminhao-basculante/</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2240/cidepsul-realiza-teste-seletivo-para-contratacao-de-operadores-de-maquinas-e-motoristas-de-caminhao-basculante</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>5</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/user/planocidadaosamas</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>http://www.youtube.com/user/planocidadaosamas</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2324/seminario-sobre-planejamento-participativo</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>5</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>http://www2.inca.gov.br/wps/wcm/connect/inca/portal/home</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>www2.inca.gov.br</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Instituto Nacional de Câncer José Alencar Gomes da Silva (INCA)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2040/outubro-rosa-diagnostico-precoce-melhora-a-resposta-ao-tratamento/</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>5</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>http://blog.saude.gov.br/</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>blog.saude.gov.br</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>http://blog.saude.gov.br/</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2040/outubro-rosa-diagnostico-precoce-melhora-a-resposta-ao-tratamento/</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>5</v>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.nfse.gov.br/EmissorNacional</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>www.nfse.gov.br</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>neste link</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2880/meis-terao-que-emitir-notas-fiscais-por-sistema-nacional-a-partir-de-abril</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>5</v>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/cuidedequemvoceama?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARD8C-_tSCjSI_AgEDWeFlOtfOXeeQNWbtLD2yasOeJbZdNkjRDqz_ERvBw5U6qSMZ8yd_5jwVQ447Bl1MVUgB-8_bg-KD-6QPhOgXD2FW5EzsM80RDmwRM3X0jVUAHxhuKagZuf4u3c3EsTu21ce9yrx6XWDp1oeKHmAbOHpYbstZuW5Izp-YA7EyljRckPg4O0OMvOoFSe0Kajlkf6rcifWysKbhD-Q9fb0_1UdM70rOX9AiH8RldT0Iamu2nAMXsAios7YBTH8cPip8E0YTkymtvx85rJTNrVRDkwaybw_pDuZtvfP_CU9xdsN9KZSSVEFsHHn0aXf6yHCerPLSqCSUsIp-x9VhqLF19jwUGN9Pay539M77S-z-e68kHw1fma5XCeXg&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>#CuideDeQuemVoceAma</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2581/vacinacao-para-idosos-de-76-e-77-anos</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>5</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:14:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://meet.google.com/dgm-cfst-grp</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>meet.google.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>https://meet.google.com/dgm-cfst-grp</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2904/conferencia-voltada-para-profissionais-da-arquitetura-e-engenharia-acontece-nesta-quinta-274</t>
+        </is>
+      </c>
+      <c r="F351" t="n">
+        <v>6</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>http://www.gazetainformativa.com.br/a-revolucao-o-poeta-o-delegado-e-o-hino/</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>www.gazetainformativa.com.br</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Gerson Cesar Souza</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2867/hino-de-sao-mateus-do-sul-completa-hoje-90-anos-de-historia</t>
+        </is>
+      </c>
+      <c r="F352" t="n">
+        <v>6</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H1rqPGRRxIo&amp;feature=youtu.be</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - INTRODUÇÃO</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F353" t="n">
+        <v>6</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AAsGr8lHV4s&amp;feature=youtu.be</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - APRESENTAÇÃO</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>6</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://youtu.be/u2Hsc601P00</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 3 CHIMARRÓDROMO</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F355" t="n">
+        <v>6</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://youtu.be/ECyh0hOE3UY</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 4 BIBLIOTECA</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F356" t="n">
+        <v>6</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://youtu.be/oZn5eAcDbCY</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 5 TIPUANA</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>6</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=U731jOYvvcc</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 6 TIPUANA COLÉGIO SÃO MATEUS</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F358" t="n">
+        <v>6</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://youtu.be/9ksyXHb-hcA</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 7 VIBURNUM</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F359" t="n">
+        <v>6</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://youtu.be/o9OkHj_mEOA</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 8 PRAÇA DA RODOVIÁRIA</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F360" t="n">
+        <v>6</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://youtu.be/etiTq_2x-J8</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 9 CANAFÍSTULA</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F361" t="n">
+        <v>6</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://youtu.be/yEarOupHiEg</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>youtu.be</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>PASSEIO DAS ÁRVORES - 10 PRAÇA DO CARVALHO</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1493/passeio-das-arvores/</t>
+        </is>
+      </c>
+      <c r="F362" t="n">
+        <v>6</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>http://www.iap.pr.gov.br/modules/conteudo/conteudo.php?conteudo=1327</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>www.iap.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>endereço</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1913/prazo-para-inscricoes-no-cadastro-ambiental-rural-se-encerra-no-proximo-dia-6/</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>6</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>http://www.iap.pr.gov.br/arquivos/File/manual_cadastro_ambiental_rural.pdf</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>www.iap.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>clique aqui para baixar o Manual</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1913/prazo-para-inscricoes-no-cadastro-ambiental-rural-se-encerra-no-proximo-dia-6/</t>
+        </is>
+      </c>
+      <c r="F364" t="n">
+        <v>6</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:52:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>http://www.agenciafiep.com.br/video/sao-mateus-do-sul-ganha-nova-unidade-do-senai/</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>www.agenciafiep.com.br</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>http://www.agenciafiep.com.br/video/sao-mateus-do-sul-ganha-nova-unidade-do-senai/</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2235/lancada-a-pedra-fundamental-da-obra-do-senai-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F365" t="n">
+        <v>6</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1rFGYL8zaLItubuecxeL7l5D5hdbosQzHg1IQYj6_bXY/viewform?edit_requested=true&amp;fbclid=IwAR2ZDFi4d7eA0EuDtWi4wLI3xnxSDH4KjB_EaaPRGAAdUA62TlzsP6-F_8c</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI PARA SE INSCREVER</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2677/prefeitura-de-sao-mateus-do-sul-abre-processo-seletivo-com-salario-de-ate-r-267346</t>
+        </is>
+      </c>
+      <c r="F366" t="n">
+        <v>6</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/1QmxNI7OopfqLy_wkNyzjVcIe2UPODZLmExFg5BnRzkQ/viewform?fbclid=IwAR0IaiGxMX1dfgXexNaUrbW0Z8HK2krK-WZX8BYg7M4FzY-aKhkt6xU1Hmc&amp;edit_requested=true</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI PARA SE INSCREVER</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2677/prefeitura-de-sao-mateus-do-sul-abre-processo-seletivo-com-salario-de-ate-r-267346</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>6</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2621/vacinacao-45-a-49-anos</t>
+        </is>
+      </c>
+      <c r="F368" t="n">
+        <v>6</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>#VacinaSamas</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2621/vacinacao-45-a-49-anos</t>
+        </is>
+      </c>
+      <c r="F369" t="n">
+        <v>6</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/cuidedequemvoceama?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBq9VXMZ5mfLdppySbFJF4UHBe0ZK9OeYO28w9lh0ylhhiOTIOx45xOMX58cgyUE8czxTsxDLzUQ3ke2F75jtDoscXJ2RDvnmN8aYPZw4kOg35ei6uUlxHVKXNHzZQH95FyNSHE3fKh5Da6WGKCmRJhbKhUu0OVZxaM9CxLv95yuYk46e9iqsoQr85BRVA53qZk91ffLrcK9v-GzgHh2Zw-fexXIWIVxM2_qOwx0J171rESV1hrO6DDzEeU2ZIj92glIH6Fv_Ih7wxU5QWKsQdp7skHLOucPKTyN751jXwJ-JHYtylHw_SnkZE6FQXVMMLyBVioqC4hNycfNKI-o5fiQ9__E7s7V519QdHc6AxGs75_9ks5S5QaQYAK0V4DrhZADDPBSQ&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>#CuideDeQuemVoceAma</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2574/vacinacao-para-idosos-de-81-e-82-anos</t>
+        </is>
+      </c>
+      <c r="F370" t="n">
+        <v>6</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/cuidedequemvoceama?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARCWbJ9JbaK9qYZwHnuOXqg7CBusefIS-qb5CeVCJSUHzEEQMErcFWmEJInSGw6tpeYcNj26asudeynQIr_n7p8B2bNoAIT8MjnjDQnGjMSxDg9ppj4SHGVtpcOIe-2b-lfshjwOgMmQazVML043IyyMfOSr7llLzN-2_3FwUCSG4cKYjgQCy5AWHsJYgHkTVYHB-H23btkdFXIjJRGFYlW1OepvnwfL4LY1FdGCgzWswAQsoeZelELXcfZSfzAuM3zTvrbbE-__Vk55R_B0DQlV0W3yt5tHEcVyPOtvltM29_02YzKryQY9HN997lRME900gcoebkJQ2hdfdHkoo_bqFHD2XwHQky8-n2NsQN3qMDmFVt2oE5ZslOs5L0yqYp_7gp4caQ&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>#CuideDeQuemVoceAma</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2572/vacinacao-para-idosos-de-83-e-84-anos</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>6</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cdweb/03112-006/contribuinte/cad_gerar_taxas.faces</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>aqui</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1243/campanha-leao-amigo-da-crianca-estimula-deducao-do-imposto-de-renda</t>
+        </is>
+      </c>
+      <c r="F372" t="n">
+        <v>6</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZUf7NJxMrNwoU_8VS84N-WyFJfVtUigRUGzxSPXgdL5yQJ7Wbr6Ef46thVbwnTeIFIXKKilbNjTnfieHb0TIzYr8fDJ0tgUeKEfcFC5IwKSGt3fZ8g9GXgHs2paWAu8UyfFO5NCK-eyG2zPK4iN1tRhiK6ZJAZbdN17nUDrbjecV4yijCepsJmB8UqL4-OhwtI&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2727/covid-19-diminui-o-tempo-de-intervalo-para-vacina-de-reforco</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>6</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__cft__[0]=AZUf7NJxMrNwoU_8VS84N-WyFJfVtUigRUGzxSPXgdL5yQJ7Wbr6Ef46thVbwnTeIFIXKKilbNjTnfieHb0TIzYr8fDJ0tgUeKEfcFC5IwKSGt3fZ8g9GXgHs2paWAu8UyfFO5NCK-eyG2zPK4iN1tRhiK6ZJAZbdN17nUDrbjecV4yijCepsJmB8UqL4-OhwtI&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>#VacinaSamas</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2727/covid-19-diminui-o-tempo-de-intervalo-para-vacina-de-reforco</t>
+        </is>
+      </c>
+      <c r="F374" t="n">
+        <v>6</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026-08-08 14:53:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://leilaopublicoparana.org/br/?fbclid=IwAR15NBhowbkUAxFhm25biGmOXgZ7LPEBFiI0dm4fNbw9JfR1xJXHeXFOgsE</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>leilaopublicoparana.org</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>https://leilaopublicoparana.org/br/</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2748/atencao-fake-news</t>
+        </is>
+      </c>
+      <c r="F375" t="n">
+        <v>6</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:59:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/cuidedequemvoceama?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDKD0Ym_8jUJzfG7Rihh3KYEEIfcckt3Ko6R1gYKy2zKz7WtIAm-e5fz8XfrfkMDc4Oi-WfGZBKvoR0J97CJIMefnHgZpGs6Y8yHsVQnS-QlxyVU_a_td7zZNYKslYy6om8PbqDS4gwRoxGKNBwPuwOU2ebYwWjmrtmd_CfHaLMj1IuIjfIljcDj_o5qeCA0YHqvNRKzrG7SiP62Ej8TcZPzeafhCjrbA8nvVrds0uufKVnAuE0uxBDSVoRw2SvENHj9aBJvzc_XTst6GgROQcUdy4BrdJ1CO-0mFsKd7t-DHRL6OxQu7-U1DnYwtF6nawPGFTvobQmM5AkRGn0NL6koneKhDUUuNgXVm3Q6eMU9V7cKyAUT70GfiHR7-03p0hIBHBn7Q&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>#CuideDeQuemVoceAma</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2571/2-dose-para-os-idosos</t>
+        </is>
+      </c>
+      <c r="F376" t="n">
+        <v>6</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2026-08-08 15:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSdH9bdT3SJldNplaKuqouCvkJ-HlNKT-A_hd1Cu6CpZ4SE-Lg/viewform?pli=1</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2957/abertas-inscricoes-para-curso-gratuito-de-mecanica-automotiva/</t>
+        </is>
+      </c>
+      <c r="F377" t="n">
+        <v>6</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:00:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>http://www.seed.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>www.seed.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>www.seed.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2255/cadastro-iesdevizivali</t>
+        </is>
+      </c>
+      <c r="F378" t="n">
+        <v>6</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:00:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>http://polouabdesomateusdosul.blogspot.com.br/</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>polouabdesomateusdosul.blogspot.com.br</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>http://polouabdesomateusdosul.blogspot.com.br/</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2255/cadastro-iesdevizivali</t>
+        </is>
+      </c>
+      <c r="F379" t="n">
+        <v>6</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:00:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/pss-edital-no-021-2019-oficial.pdf</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>PSS Edital nº 021/2019 OFICIAL.</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1091/prefeitura-de-sao-mateus-do-sul-realizara-novo-processo-seletivo-para-a-contratacao-de-estagiarios</t>
+        </is>
+      </c>
+      <c r="F380" t="n">
+        <v>6</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/errata-conteudos-edital-021-2019-1.pdf</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Errata CONTEÚDOS edital 021-2019.</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1091/prefeitura-de-sao-mateus-do-sul-realizara-novo-processo-seletivo-para-a-contratacao-de-estagiarios</t>
+        </is>
+      </c>
+      <c r="F381" t="n">
+        <v>6</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/errata-edital-021-2019-alteracoes-1.pdf</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>ERRATA - Edital 021-2019 - alterações.</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1091/prefeitura-de-sao-mateus-do-sul-realizara-novo-processo-seletivo-para-a-contratacao-de-estagiarios</t>
+        </is>
+      </c>
+      <c r="F382" t="n">
+        <v>6</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:30:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/resolucao-no-13-publicacao-curso-preparatorio.pdf</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Resolução nº 13 - Publicação Curso Preparatório</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1095/candidatos-ao-conselho-tutelar-de-sao-mateus-do-sul-participarao-de-curso-preparatorio</t>
+        </is>
+      </c>
+      <c r="F383" t="n">
+        <v>6</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:30:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/diario-oficial-2089-03.07.2019-1.pdf</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Diario Oficial - 2089-03.07.2019</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1095/candidatos-ao-conselho-tutelar-de-sao-mateus-do-sul-participarao-de-curso-preparatorio</t>
+        </is>
+      </c>
+      <c r="F384" t="n">
+        <v>6</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:30:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>http://www.saude.pr.gov.br/arquivos/File/---_Resolucoes2018/465_18.PDF</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>www.saude.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Resolução SESA nº 465/2018</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1229/municipio-busca-recursos-para-equipagem-do-hospital-e-maternidade-dr-paulo-fortes</t>
+        </is>
+      </c>
+      <c r="F385" t="n">
+        <v>6</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:38:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>http://www.ticketagora.com.br/Evento/2525/1+MEIA+MARATONA+CIDADE+DE+SAO+MATEUS+DO+SUL++2015.aspx?origem=assessocor</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>www.ticketagora.com.br</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>site da prova</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1700/inscricoes-abertas-para-a-1-meia-maratona-cidade-de-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F386" t="n">
+        <v>6</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:39:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>http://www.difusoradoxisto.com.br/</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>www.difusoradoxisto.com.br</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>site da rádio Difusora do Xisto</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1733/sao-mateus-do-sul-sedia-etapa-macrorregional-do-torneio-bom-de-bola/</t>
+        </is>
+      </c>
+      <c r="F387" t="n">
+        <v>6</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:39:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>http://www.jogosabertos.pr.gov.br/modules/fase_final/uploads/2015_japs_reg10_boletim_resultados_31_07_a_02_08_15.pdf</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>www.jogosabertos.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>clique aqui (site da SEET)</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1799/galeria-atletas-disputam-sete-modalidades-esportivas-pela-fase-regional-dos-japs/</t>
+        </is>
+      </c>
+      <c r="F388" t="n">
+        <v>6</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:39:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>http://www.jogosabertos.pr.gov.br/modules/fase_final/uploads/japs_divb_boletim_informativo_reg_10.pdf</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>www.jogosabertos.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Clique aqui</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1803/municipio-recebe-mais-de-26-mil-atletas-para-fase-regional-dos-japs-neste-final-de-semana/</t>
+        </is>
+      </c>
+      <c r="F389" t="n">
+        <v>6</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:39:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>http://www.jogosescolares.pr.gov.br/modules/fase_final/uploads/smsu_classificacao_final_geral.pdf</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>www.jogosescolares.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Clique aqui.</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1835/galeria-macrorregional-dos-jeps-movimenta-sao-mateus-do-sul-no-final-de-semana/</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>6</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>http://www.jogosescolares.pr.gov.br/modules/fase_final/uploads/smsu_boletim_de_programacao.pdf</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>www.jogosescolares.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Veja aqui a programação completa da fase macrorregional dos 62º Jogos Escolares do Paraná</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1837/sao-mateus-do-sul-sedia-fase-macrorregional-dos-62-jogos-escolares-do-parana/</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>6</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:39:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/santizacao?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBu6k_TOpPXaISbYCXJGOs2F-IbfWvQ1bAfqKW4HRG2lvzI3Nkoyx3ZdbJz6-mZND75vsxbTZ6D948JxQxW-3kTK7flvcNYH6-aCX0GKikernNTT4tDVSn90o45lOzHLnRvngO7SMGES8iF73RL97DsnjtIFm-DiohWOjfDgM2W-xxGVMVDaVOeszNGKlx3l7C2xPXOyjyjYIjT8PispNXBUwoSaN40JuZOjIECypOcUmU9HVWZCoxyrx1yEbQ50KW1dB2wpLW9hBi6D0pnD05XuqUt1-lenfjAl8RQOeEeIE9bno3y8hc&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>#Santizacao</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2578/sanitizacao-em-predios-publicos</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>6</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:41:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/saomateusdosulcontraacovid?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBu6k_TOpPXaISbYCXJGOs2F-IbfWvQ1bAfqKW4HRG2lvzI3Nkoyx3ZdbJz6-mZND75vsxbTZ6D948JxQxW-3kTK7flvcNYH6-aCX0GKikernNTT4tDVSn90o45lOzHLnRvngO7SMGES8iF73RL97DsnjtIFm-DiohWOjfDgM2W-xxGVMVDaVOeszNGKlx3l7C2xPXOyjyjYIjT8PispNXBUwoSaN40JuZOjIECypOcUmU9HVWZCoxyrx1yEbQ50KW1dB2wpLW9hBi6D0pnD05XuqUt1-lenfjAl8RQOeEeIE9bno3y8hc&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>#SaoMateusdoSulContraaCOVID</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2578/sanitizacao-em-predios-publicos</t>
+        </is>
+      </c>
+      <c r="F393" t="n">
+        <v>6</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:41:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/servidorpublico/login.faces</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Betha Servidor</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1470/servidor-publico-retire-o-seu-informe-de-rendimentos</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>6</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:41:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/infosamas/videos/330209014060530/</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Confira o vídeo com a Entrevista</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1447/secretario-de-infraestrutura-e-logistica-do-estado-pepe-richa-traz-boas-noticias-a-sao-mateus-do-sul-e-regiao</t>
+        </is>
+      </c>
+      <c r="F395" t="n">
+        <v>6</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>http://www.aen.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>www.aen.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1464/estrada-que-liga-irati-a-sao-mateus-do-sul-vai-ser-pavimentada</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>6</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:42:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://wa.me/5542988371655</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>wa.me</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>WhatsApp da Defesa Civil: (42) 98837-1655</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/3019/chuvas-defesa-civil-acompanha-situacao-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F397" t="n">
+        <v>6</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:42:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>http://www.cieepr.org.br/?fbclid=IwAR2t4r9SeQEBYAl20_5SMOd_TzReUf6OsEJi4qmtAEEAmzLzEAFw_C_zyo8</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>www.cieepr.org.br</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>www.cieepr.org.br</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2472/prova-do-pss-da-prefeitura-municipal-acontece-no-sabado-25</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>6</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:42:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>http://moradasaberes.org/</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>moradasaberes.org</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Conheça o site do projeto Morada dos Saberes.</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1769/rapidas-prefeitura-finaliza-melhorias-no-parque-de-exposicoes-morada-dos-saberes-inaugura-sede/</t>
+        </is>
+      </c>
+      <c r="F399" t="n">
+        <v>6</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:44:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/programacao-jeps.pdf</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Programação JEPS;</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1099/sao-mateus-do-sul-sedia-a-fase-macrorregional-do-66-jogos-escolares-do-parana-entre-os-dias-27-e-30-de-junho</t>
+        </is>
+      </c>
+      <c r="F400" t="n">
+        <v>6</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:44:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/programacao-atletismo.pdf</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Programação Atletismo;</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1099/sao-mateus-do-sul-sedia-a-fase-macrorregional-do-66-jogos-escolares-do-parana-entre-os-dias-27-e-30-de-junho</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>6</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:44:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/cronograma-modalidades.pdf</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Cronograma Modalidades</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1099/sao-mateus-do-sul-sedia-a-fase-macrorregional-do-66-jogos-escolares-do-parana-entre-os-dias-27-e-30-de-junho</t>
+        </is>
+      </c>
+      <c r="F402" t="n">
+        <v>6</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:44:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/locais-de-competicao.pdf</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Locais de Competição</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1099/sao-mateus-do-sul-sedia-a-fase-macrorregional-do-66-jogos-escolares-do-parana-entre-os-dias-27-e-30-de-junho</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>6</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-08-08 16:44:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://www.planalto.gov.br/ccivil_03/_Ato2019-2022/2020/Lei/L2960.htm</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>LEI Nº 2.960, DE 14 DE JULHO DE 2020</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/leis_decretos/17348/</t>
+        </is>
+      </c>
+      <c r="F404" t="n">
+        <v>6</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-08-08 18:33:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=0B89WOtUF3JMla1IzbzBHejBiUW8</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>CLIQUE AQUI PARA CONHECER E BAIXAR O LIVRO</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1557/faca-o-download-do-livro-didatico</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>6</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:21:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>http://www.cps.uepg.br/uab/documentos/2013/2013_MANUAL_VESTIBULAR_EAD.pdf</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>www.cps.uepg.br</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>EDITAL</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2239/licenciatura-em-matematica-a-distancia--uepguab</t>
+        </is>
+      </c>
+      <c r="F406" t="n">
+        <v>6</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:21:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>http://www.uepg.br/ead</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>www.uepg.br</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>www.uepg.br/ead</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2239/licenciatura-em-matematica-a-distancia--uepguab</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>6</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:21:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polouabsaomateusdosul?ref=hl</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/polouabsaomateusdosul?ref=hl</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2079/inscricoes-para-selecao-de-tutores---especializacoes-em-gestao-publica-e-gestao-em-saude</t>
+        </is>
+      </c>
+      <c r="F408" t="n">
+        <v>6</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>http://sites.unicentro.br/uab/blog/editais/edital-no-0192014-inscricoes-para-selecao-de-tutores-especializacoes-em-gestao-publica-gestao-publica-municipal-e-gestao-em-saude/</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>sites.unicentro.br</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>http://sites.unicentro.br/uab/blog/editais/edital-no-0192014-inscricoes-para-selecao-de-tutores-especializacoes-em-gestao-publica-gestao-publica-municipal-e-gestao-em-saude/</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2079/inscricoes-para-selecao-de-tutores---especializacoes-em-gestao-publica-e-gestao-em-saude</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>6</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:21:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>http://www.brasil.gov.br/eu-vou/homens-so-procuram-o-medico-por-influencia-da-mulher-ou-de-filhos-revela-pesquisa</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>www.brasil.gov.br</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>no ano passado</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1789/encontros-discutem-saude-do-homem-durante-o-agosto-azul/</t>
+        </is>
+      </c>
+      <c r="F410" t="n">
+        <v>6</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:22:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/prefsamas?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARAJxmme6NyrhEna1s1Oszzc7tKp6VT-0LkBBIO_dYYam038zo5K0BVkxI6T-UaM5U-pZ8zFnfCJOq8QMexDjD8fLrpYx9nfQeJ0ofd_aJspCmKYD8wHQWrciCTDZ2pyrRUJYttnyotAEFPcKP0KkFOKtcJ6K7y7xINE4d2Qc3TBf9LOs5NgxVk2Dmo4vbh1jR-Uq7QmyaZZg28mOakgfm7b_mOFl5red0MeRPw106MDKqwYnavWdkFCHONMmUzHPRzy_CeYIX7ag-RKKcVpaufWHImJK4tRTFitzsEaXEumLvtr0D8BQuFEZpdIJYnRnp7l2Y-mZoEeJLgiRdol9ccpl2xT&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>#PrefSamas</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2518/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>6</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/informeinstitucional?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARAJxmme6NyrhEna1s1Oszzc7tKp6VT-0LkBBIO_dYYam038zo5K0BVkxI6T-UaM5U-pZ8zFnfCJOq8QMexDjD8fLrpYx9nfQeJ0ofd_aJspCmKYD8wHQWrciCTDZ2pyrRUJYttnyotAEFPcKP0KkFOKtcJ6K7y7xINE4d2Qc3TBf9LOs5NgxVk2Dmo4vbh1jR-Uq7QmyaZZg28mOakgfm7b_mOFl5red0MeRPw106MDKqwYnavWdkFCHONMmUzHPRzy_CeYIX7ag-RKKcVpaufWHImJK4tRTFitzsEaXEumLvtr0D8BQuFEZpdIJYnRnp7l2Y-mZoEeJLgiRdol9ccpl2xT&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>#InformeInstitucional</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2518/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F412" t="n">
+        <v>6</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/todoscontracovid19?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARAJxmme6NyrhEna1s1Oszzc7tKp6VT-0LkBBIO_dYYam038zo5K0BVkxI6T-UaM5U-pZ8zFnfCJOq8QMexDjD8fLrpYx9nfQeJ0ofd_aJspCmKYD8wHQWrciCTDZ2pyrRUJYttnyotAEFPcKP0KkFOKtcJ6K7y7xINE4d2Qc3TBf9LOs5NgxVk2Dmo4vbh1jR-Uq7QmyaZZg28mOakgfm7b_mOFl5red0MeRPw106MDKqwYnavWdkFCHONMmUzHPRzy_CeYIX7ag-RKKcVpaufWHImJK4tRTFitzsEaXEumLvtr0D8BQuFEZpdIJYnRnp7l2Y-mZoEeJLgiRdol9ccpl2xT&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>#TodosContraCovid19</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2518/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F413" t="n">
+        <v>6</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/governodoparan%C3%A1?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARAJxmme6NyrhEna1s1Oszzc7tKp6VT-0LkBBIO_dYYam038zo5K0BVkxI6T-UaM5U-pZ8zFnfCJOq8QMexDjD8fLrpYx9nfQeJ0ofd_aJspCmKYD8wHQWrciCTDZ2pyrRUJYttnyotAEFPcKP0KkFOKtcJ6K7y7xINE4d2Qc3TBf9LOs5NgxVk2Dmo4vbh1jR-Uq7QmyaZZg28mOakgfm7b_mOFl5red0MeRPw106MDKqwYnavWdkFCHONMmUzHPRzy_CeYIX7ag-RKKcVpaufWHImJK4tRTFitzsEaXEumLvtr0D8BQuFEZpdIJYnRnp7l2Y-mZoEeJLgiRdol9ccpl2xT&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>#GovernoDoParaná</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2518/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F414" t="n">
+        <v>6</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/minist%C3%A9riodasa%C3%BAde?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARAJxmme6NyrhEna1s1Oszzc7tKp6VT-0LkBBIO_dYYam038zo5K0BVkxI6T-UaM5U-pZ8zFnfCJOq8QMexDjD8fLrpYx9nfQeJ0ofd_aJspCmKYD8wHQWrciCTDZ2pyrRUJYttnyotAEFPcKP0KkFOKtcJ6K7y7xINE4d2Qc3TBf9LOs5NgxVk2Dmo4vbh1jR-Uq7QmyaZZg28mOakgfm7b_mOFl5red0MeRPw106MDKqwYnavWdkFCHONMmUzHPRzy_CeYIX7ag-RKKcVpaufWHImJK4tRTFitzsEaXEumLvtr0D8BQuFEZpdIJYnRnp7l2Y-mZoEeJLgiRdol9ccpl2xT&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>#MinistérioDaSaúde</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2518/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F415" t="n">
+        <v>6</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/prefsamas?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDukmp4RVBuHNXOOWz7I4IrNlo-mOUKKrvTKl2XXIOJrvrbJVzczLmU0Ea5DKVv_qn33DRWxZhAIuVUWQQZDCxGVkeTmpE23efksGDqwVi-OsVTYhq6YSxSIsXJT6vwlZn3mn-TboqJJbGW98VfkHPEzAPQcuKk1BeVDkBYetm1kd3FO8XuC-y2zCxQrgXg0DozAjASJcy0f1AK_MXaPXn0K5_IC1sPyz45rhyWwK4QNVTZeG8DPi-K6kSYI46DUfVMoaKijRs9eOtCHv_6xxRrXC9xvekoil161A8tOdqFle8oBEbSm0cZvyVdf9--mwQsukUzIBAxrcVwAMPrDdzUtqLe&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>#PrefSamas</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2516/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul-0108</t>
+        </is>
+      </c>
+      <c r="F416" t="n">
+        <v>6</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/informeinstitucional?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDukmp4RVBuHNXOOWz7I4IrNlo-mOUKKrvTKl2XXIOJrvrbJVzczLmU0Ea5DKVv_qn33DRWxZhAIuVUWQQZDCxGVkeTmpE23efksGDqwVi-OsVTYhq6YSxSIsXJT6vwlZn3mn-TboqJJbGW98VfkHPEzAPQcuKk1BeVDkBYetm1kd3FO8XuC-y2zCxQrgXg0DozAjASJcy0f1AK_MXaPXn0K5_IC1sPyz45rhyWwK4QNVTZeG8DPi-K6kSYI46DUfVMoaKijRs9eOtCHv_6xxRrXC9xvekoil161A8tOdqFle8oBEbSm0cZvyVdf9--mwQsukUzIBAxrcVwAMPrDdzUtqLe&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>#InformeInstitucional</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2516/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul-0108</t>
+        </is>
+      </c>
+      <c r="F417" t="n">
+        <v>6</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/todoscontracovid19?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDukmp4RVBuHNXOOWz7I4IrNlo-mOUKKrvTKl2XXIOJrvrbJVzczLmU0Ea5DKVv_qn33DRWxZhAIuVUWQQZDCxGVkeTmpE23efksGDqwVi-OsVTYhq6YSxSIsXJT6vwlZn3mn-TboqJJbGW98VfkHPEzAPQcuKk1BeVDkBYetm1kd3FO8XuC-y2zCxQrgXg0DozAjASJcy0f1AK_MXaPXn0K5_IC1sPyz45rhyWwK4QNVTZeG8DPi-K6kSYI46DUfVMoaKijRs9eOtCHv_6xxRrXC9xvekoil161A8tOdqFle8oBEbSm0cZvyVdf9--mwQsukUzIBAxrcVwAMPrDdzUtqLe&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>#TodosContraCovid19</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2516/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul-0108</t>
+        </is>
+      </c>
+      <c r="F418" t="n">
+        <v>6</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/governodoparan%C3%A1?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDukmp4RVBuHNXOOWz7I4IrNlo-mOUKKrvTKl2XXIOJrvrbJVzczLmU0Ea5DKVv_qn33DRWxZhAIuVUWQQZDCxGVkeTmpE23efksGDqwVi-OsVTYhq6YSxSIsXJT6vwlZn3mn-TboqJJbGW98VfkHPEzAPQcuKk1BeVDkBYetm1kd3FO8XuC-y2zCxQrgXg0DozAjASJcy0f1AK_MXaPXn0K5_IC1sPyz45rhyWwK4QNVTZeG8DPi-K6kSYI46DUfVMoaKijRs9eOtCHv_6xxRrXC9xvekoil161A8tOdqFle8oBEbSm0cZvyVdf9--mwQsukUzIBAxrcVwAMPrDdzUtqLe&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>#GovernoDoParaná</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2516/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul-0108</t>
+        </is>
+      </c>
+      <c r="F419" t="n">
+        <v>6</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/minist%C3%A9riodasa%C3%BAde?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDukmp4RVBuHNXOOWz7I4IrNlo-mOUKKrvTKl2XXIOJrvrbJVzczLmU0Ea5DKVv_qn33DRWxZhAIuVUWQQZDCxGVkeTmpE23efksGDqwVi-OsVTYhq6YSxSIsXJT6vwlZn3mn-TboqJJbGW98VfkHPEzAPQcuKk1BeVDkBYetm1kd3FO8XuC-y2zCxQrgXg0DozAjASJcy0f1AK_MXaPXn0K5_IC1sPyz45rhyWwK4QNVTZeG8DPi-K6kSYI46DUfVMoaKijRs9eOtCHv_6xxRrXC9xvekoil161A8tOdqFle8oBEbSm0cZvyVdf9--mwQsukUzIBAxrcVwAMPrDdzUtqLe&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>#MinistérioDaSaúde</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2516/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul-0108</t>
+        </is>
+      </c>
+      <c r="F420" t="n">
+        <v>6</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026-08-09 09:57:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fernanda.sardanha/photos/pcb.1193615504411228/1193615384411240/?__cft__[0]=AZVtoxwWzv0tyz2O3xFSOYT6lrWUQM5eQkpAn-PF1V5dIssrTIaFsUXdwF9giNUWpnnIBvhgVCTPxJ7y_On-t-uNJZ81PywD0zOiT6Y4Er0SBH_7RrgpiY9A_QTH1SkOuDhESvJOuUiCcKtqN1TREb1-kHMSAsWEMpxQxnIub5FD1RNSIFLYfu0hoDJzWP2esHw&amp;__tn__=*bH-R</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2655/novo-local-para-unidade-sentinela/</t>
+        </is>
+      </c>
+      <c r="F421" t="n">
+        <v>6</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fernanda.sardanha/photos/pcb.1193615504411228/1193615367744575/?__cft__[0]=AZVtoxwWzv0tyz2O3xFSOYT6lrWUQM5eQkpAn-PF1V5dIssrTIaFsUXdwF9giNUWpnnIBvhgVCTPxJ7y_On-t-uNJZ81PywD0zOiT6Y4Er0SBH_7RrgpiY9A_QTH1SkOuDhESvJOuUiCcKtqN1TREb1-kHMSAsWEMpxQxnIub5FD1RNSIFLYfu0hoDJzWP2esHw&amp;__tn__=*bH-R</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2655/novo-local-para-unidade-sentinela/</t>
+        </is>
+      </c>
+      <c r="F422" t="n">
+        <v>6</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fernanda.sardanha/photos/pcb.1193615504411228/1193615364411242/?__cft__[0]=AZVtoxwWzv0tyz2O3xFSOYT6lrWUQM5eQkpAn-PF1V5dIssrTIaFsUXdwF9giNUWpnnIBvhgVCTPxJ7y_On-t-uNJZ81PywD0zOiT6Y4Er0SBH_7RrgpiY9A_QTH1SkOuDhESvJOuUiCcKtqN1TREb1-kHMSAsWEMpxQxnIub5FD1RNSIFLYfu0hoDJzWP2esHw&amp;__tn__=*bH-R</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2655/novo-local-para-unidade-sentinela/</t>
+        </is>
+      </c>
+      <c r="F423" t="n">
+        <v>6</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/fernanda.sardanha/photos/pcb.1193615504411228/1193615374411241/?__cft__[0]=AZVtoxwWzv0tyz2O3xFSOYT6lrWUQM5eQkpAn-PF1V5dIssrTIaFsUXdwF9giNUWpnnIBvhgVCTPxJ7y_On-t-uNJZ81PywD0zOiT6Y4Er0SBH_7RrgpiY9A_QTH1SkOuDhESvJOuUiCcKtqN1TREb1-kHMSAsWEMpxQxnIub5FD1RNSIFLYfu0hoDJzWP2esHw&amp;__tn__=*bH-R</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2655/novo-local-para-unidade-sentinela/</t>
+        </is>
+      </c>
+      <c r="F424" t="n">
+        <v>6</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZWn8ppsF7w5MInfO4Ja05HCkCWAH9nJSWPqPImsVOwV8pbECDw9iM5Lo4hIOi068FNYzRbxVr7UFQErw5C6CTFP1hyBX8Wp7wDTgfLMbZ96nLSxj9DhkTDC2XjHG2gBVhts0TF716Fm1zSsCYFrzDhQEqXjhVEEkhoi7ewakn-WIRPNv120x0_tUBz5m47jHcU&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2651/vacinacao-46-anos-sem-comorbidades/</t>
+        </is>
+      </c>
+      <c r="F425" t="n">
+        <v>6</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__cft__[0]=AZWn8ppsF7w5MInfO4Ja05HCkCWAH9nJSWPqPImsVOwV8pbECDw9iM5Lo4hIOi068FNYzRbxVr7UFQErw5C6CTFP1hyBX8Wp7wDTgfLMbZ96nLSxj9DhkTDC2XjHG2gBVhts0TF716Fm1zSsCYFrzDhQEqXjhVEEkhoi7ewakn-WIRPNv120x0_tUBz5m47jHcU&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>#VacinaSamas</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2651/vacinacao-46-anos-sem-comorbidades/</t>
+        </is>
+      </c>
+      <c r="F426" t="n">
+        <v>6</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:09:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/hashtag/otrabalhonaopara?source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBnefn9BrISw6fodCzWoS6yt7ghKUhESN2-1_i_myRSWljk9sf9mGR3pMorhMCnSuqRpyZj575re-zlYciabnwwhMQKCrozDuE0gQViNk_GrKgDQn_GkvIsT_JLbQYFJF5f3fJielqSStmfZUdm6RF-a4LgvvRJQf4y3LWdRJbHVy0YB68S6UeBMMl-IaeSQXUNZrbLvSiciM34DiqiofJ4jVaNfKZDYmUQhFDl9EkygpcXTtH-ogFxhHjAjRdpTHAAEYjMyypcXjAVp4jdwGIUoGL8n5LRU_nhIjIe1ZWGARrHB_k0m2Hrsk2ZrWrh6QQ&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>business.facebook.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>#OTrabalhoNaoPara</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2555/uma-segunda-chance-para-jovem-sao-mateuense</t>
+        </is>
+      </c>
+      <c r="F427" t="n">
+        <v>7</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:10:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/resultado-preliminar-2-etapa-conselho-tutelar-2019.pdf</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>RESULTADO PRELIMINAR 2 ETAPA CONSELHO TUTELAR 2019</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1086/cmdca-divulga-resultado-da-prova-realizada-pelos-candidatos-ao-cargo-de-conselheiro-tutelar</t>
+        </is>
+      </c>
+      <c r="F428" t="n">
+        <v>7</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:10:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://ead.uepg.br/apl/sigma/assets/editais/PS0306E0617.pdf</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>ead.uepg.br</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>pré-requisitos</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1846/uepg-abre-inscricoes-para-tutor-bolsista-de-curso-de-gestao-educacional</t>
+        </is>
+      </c>
+      <c r="F429" t="n">
+        <v>7</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>http://www.facebook.com/PrefeituraSMS</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>www.facebook.com/PrefeituraSMS</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1915/siga-a-prefeitura-nas-redes-sociais</t>
+        </is>
+      </c>
+      <c r="F430" t="n">
+        <v>7</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>http://www.twitter.com/PrefeituraSMS</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>www.twitter.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>www.twitter.com/PrefeituraSMS</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1915/siga-a-prefeitura-nas-redes-sociais</t>
+        </is>
+      </c>
+      <c r="F431" t="n">
+        <v>7</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/PrefeituraSMS</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>www.instagram.com/PrefeituraSMS</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1915/siga-a-prefeitura-nas-redes-sociais</t>
+        </is>
+      </c>
+      <c r="F432" t="n">
+        <v>7</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>http://www.sesa.pr.gov.br/</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>www.sesa.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>www.sesa.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2231/vigilancia-sanitaria-realiza-palestra-de-orientacao-para-comercio-varejista-de-alimentos</t>
+        </is>
+      </c>
+      <c r="F433" t="n">
+        <v>7</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cidadaoweb3/resource.faces?params=HC6Vd71zH4m2clcUtQU-5w==</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Emissão de 2ª via de carnes”</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1307/carnes-do-alvara-licenca-sanitaria-e-iss-2018-podem-ser-retirados-na-prefeitura-ou-na-internet</t>
+        </is>
+      </c>
+      <c r="F434" t="n">
+        <v>7</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cidadaoweb3/03015-029/main.faces</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Emitir</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1307/carnes-do-alvara-licenca-sanitaria-e-iss-2018-podem-ser-retirados-na-prefeitura-ou-na-internet</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>7</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2026-08-09 10:11:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZVJzBM8yNhUJTmGQdr9JyFb66if1AfNkUvoUjelSZiDKxtTYwYKzm_FZw6iuCvdEKqEvkC1gfgNl_cHA5b1UObIOqep9GXUCsLd7hnNzc8D86C2oM37VoKTwYw859-mbiqZCCllN-KG5NZZ3Dl8DOulEINKtnf2BOpNcUYgLE1Z6fDZ4jSh9nQGD7HELKkUyr0&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2654/vacinacao-41-e-42-anos-sem-comorbidades</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>7</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:27:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__cft__[0]=AZVJzBM8yNhUJTmGQdr9JyFb66if1AfNkUvoUjelSZiDKxtTYwYKzm_FZw6iuCvdEKqEvkC1gfgNl_cHA5b1UObIOqep9GXUCsLd7hnNzc8D86C2oM37VoKTwYw859-mbiqZCCllN-KG5NZZ3Dl8DOulEINKtnf2BOpNcUYgLE1Z6fDZ4jSh9nQGD7HELKkUyr0&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>#VacinaSamas</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2654/vacinacao-41-e-42-anos-sem-comorbidades</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>7</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:27:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZVT2dOoeRt8uery_yWTJDqzm32uIOFcpzrUZxsLZeos9FY_QZct5GO3qWvci-wCqO4RJWxwoKTewEcRU5Mfi3A-Eei3KR8aO4muyzmUGA2oO6JB3xEgM9zGWgyFMmEjS4BZZiMMX7on1x2WxTBEDUuiSE3fLPrKkawoR_tqD9uDNiFm9TY3ozwfxuE6MNBzaZI&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2652/vacinacao-45-anos-sem-comorbidades</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>7</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:27:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>http://www.cieepr.org.br/?fbclid=IwAR3E9G0wDkzVjiakQjUsXVpu54m0-3-bDyBE-6nRc-R8BfW-F3x8VMN1LBg</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>www.cieepr.org.br</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>www.cieepr.org.br</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1164/as-inscricoes-para-estagio-na-prefeitura-municipal-de-sao-mateus-do-sul-encerram-nesta-sexta-feira-5</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>7</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:27:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/07/pmai-sao-mateus-do-sul-digital.pdf</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Arquivo Digital do PMAI São Mateus do Sul.</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1085/programa-municipal-para-atracao-de-investimentos-e-apresentado-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>7</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:28:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/06/nota-de-esclarecimento-balsa.pdf</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>NOTA DE ESCLARECIMENTO BALSA;</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1121/nota-de-esclarecimento-balsa</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>7</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:29:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cdweb/03114-005/contribuinte/rel_guiaiptu.faces</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>aqui)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1194/iptu-2019-ja-esta-liberado-para-emissao-online</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>7</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:30:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://www.pr.senac.br/trabalhe_conosco/</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>www.pr.senac.br</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>www.pr.senac.br/trabalhe_conosco/</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1537/senac-tem-vaga-para-tecnico-de-educacao-profissional-e-tecnologica</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>7</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:30:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>http://http://www.saomateusdosul.pr.gov.br/categorias/educacao-e-cultura/</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>http:</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Leia mais sobre Educação em São Mateus do Sul</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1572/estudantes-do-pontilhao-e-do-emboque-realizaram-juri-simulado-em-visita-na-sede-dos-tres-poderes</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>7</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:30:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>http://basenacionalcomum.mec.gov.br/</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>basenacionalcomum.mec.gov.br</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Saiba mais sobre a Base Nacional Comum</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1669/educacao-publica-de-sao-mateus-do-sul-discute-base-nacional-comum-curricular</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>7</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:30:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>http://legislacao.planalto.gov.br/legisla/legislacao.nsf/Viw_Identificacao/lcp%20150-2015?OpenDocument</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>legislacao.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Saiba mais.</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1734/sao-mateus-do-sul-da-inicio-a-formacao-de-primeira-turma-de-cuidadores-de-idosos</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>7</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:30:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>http://concurso.uniuv.edu.br/concursos/arquivos/concurso_000069/edital%201292015%20%20resultado%20final%20parcial%20apos%20recursos_2015-29-05_173738.pdf</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>concurso.uniuv.edu.br</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>neste link</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1862/divulgado-o-resultado-final-do-concurso-para-a-prefeitura</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>7</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:31:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://www.portaldoempreendedor.gov.br/temas/ja-sou/servicos/saiba-mais-sobre-a-suspensao-de-inscricao-do-mei/suspensao</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>www.portaldoempreendedor.gov.br</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>aqui</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1349/governo-divulga-cnpj-suspensos-e-orienta-regularizacao-de-mei</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>7</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:31:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>http://www.compredopequeno.com.br/</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>www.compredopequeno.com.br</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>www.compredopequeno.com.br</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1736/prefeitura-adere-a-campanha-do-sebrae-e-incentiva-compras-em-pequenas-empresas</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>7</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:31:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>http://www.consignet.com.br/saomateusdosul</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>www.consignet.com.br</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>ConsigNet</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1787/prefeitura-moderniza-sistema-de-controle-financeiro-para-servidores-municipais</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>7</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>2026-08-09 11:31:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>http://www.sic.cultura.pr.gov.br/cadastro/agente.php</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>www.sic.cultura.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>www.sic.cultura.pr.gov.br/cadastro/agente.php</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2521/estao-abertas-as-inscricoes-para-a-solicitacao-do-subsidio-para-manutencao-de-espacos-culturais-da-lei-aldir-blanc/</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>7</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:25:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/per%C3%ADodoeleitoral?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBlTOBTzPwNZKhpjHTnO0zp5EvRXXKKjMejl0z0KML5XhuI0PlcmPZeb8ihyEzNymOoaGwyJ9y-5WOuMhj2I9K7mwxJ-2HleTHmWRFMnGzJ2HnNXcrw_oRTvfaxAswpu-o7BZ8IwJJNkEme5OFfBtrUl8HUJy30FPWmAOjbCmQLMjvUs-EbwjLjhF-LUq2sX1v78bcbhKM7xWYrZQAl3YUY4vwU9s5iWRdLcZdk1FAcVOMCMLTcrYlsGvUVwntqFxuST9tLlPi0OfZ42dMiObvasfwMvbMXdVR78iJpGnqjRIfTGQwx-UqafRH6mMDt-loWddUphE6p7paLzd2Ml_p2g6x7&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>#PeríodoEleitoral</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2519/comunicado-oficial/</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>7</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:25:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/prefsamas?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBlTOBTzPwNZKhpjHTnO0zp5EvRXXKKjMejl0z0KML5XhuI0PlcmPZeb8ihyEzNymOoaGwyJ9y-5WOuMhj2I9K7mwxJ-2HleTHmWRFMnGzJ2HnNXcrw_oRTvfaxAswpu-o7BZ8IwJJNkEme5OFfBtrUl8HUJy30FPWmAOjbCmQLMjvUs-EbwjLjhF-LUq2sX1v78bcbhKM7xWYrZQAl3YUY4vwU9s5iWRdLcZdk1FAcVOMCMLTcrYlsGvUVwntqFxuST9tLlPi0OfZ42dMiObvasfwMvbMXdVR78iJpGnqjRIfTGQwx-UqafRH6mMDt-loWddUphE6p7paLzd2Ml_p2g6x7&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>#PrefSamas</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2519/comunicado-oficial/</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>7</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:25:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/informeinstitucional?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARBlTOBTzPwNZKhpjHTnO0zp5EvRXXKKjMejl0z0KML5XhuI0PlcmPZeb8ihyEzNymOoaGwyJ9y-5WOuMhj2I9K7mwxJ-2HleTHmWRFMnGzJ2HnNXcrw_oRTvfaxAswpu-o7BZ8IwJJNkEme5OFfBtrUl8HUJy30FPWmAOjbCmQLMjvUs-EbwjLjhF-LUq2sX1v78bcbhKM7xWYrZQAl3YUY4vwU9s5iWRdLcZdk1FAcVOMCMLTcrYlsGvUVwntqFxuST9tLlPi0OfZ42dMiObvasfwMvbMXdVR78iJpGnqjRIfTGQwx-UqafRH6mMDt-loWddUphE6p7paLzd2Ml_p2g6x7&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>#InformeInstitucional</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2519/comunicado-oficial/</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>7</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:25:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>http://www.cps.uepg.br/ead.</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>www.cps.uepg.br</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>site da Coordenadoria de Processos de Seleção (CPS)</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1504/vestibular-da-uepg-para-cursos-a-distancia-abre-prazo-de-inscricoes/</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>7</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:26:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>http://g1.globo.com/pr/parana/educacao/universidade/uepg.html</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>g1.globo.com</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>UEPG</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1504/vestibular-da-uepg-para-cursos-a-distancia-abre-prazo-de-inscricoes/</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>7</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:26:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>http://www.alistamento.eb.mil.br/</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>www.alistamento.eb.mil.br</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>www.alistamento.eb.mil.br</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1586/alistamento-militar-obrigatorio-deve-ser-feito-diretamente-pela-internet/</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>7</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:26:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>http://agenciabrasil.ebc.com.br/geral/noticia/2015-12/brasil-vai-enfrentar-primeiro-verao-com-dengue-chikungunya-e-zika</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>agenciabrasil.ebc.com.br</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Brasil vai enfrentar primeiro verão com dengue, chikungunya e Zika</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1658/municipio-debate-acoes-intensivas-de-prevencao-e-combate-ao-aedes-aegypti/</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>7</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:29:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saomateusdosul/inventario_externos.xlsx
+++ b/resultados/saomateusdosul/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:G483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16396,6 +16396,881 @@
         </is>
       </c>
     </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://www.saude.gov.br/sarampo</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>www.saude.gov.br</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>sarampo</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2481/medidas-de-prevencao-contra-o-coronavirus--covid-19</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>7</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:29:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://docs.google.com/forms/d/e/1FAIpQLSfTFRE_gJff81kdAVNyApxVhGqh-5Y7-EK_V3wIQe6FeUvyvQ/viewform</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>docs.google.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>clicando aqui</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1256/novo-canal-de-solicitacao-de-servicos-de-iluminacao-publica</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>8</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:37:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>http://www.espacoexcentrico.com.br</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>www.espacoexcentrico.com.br</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>espacoexcentrico.com.br</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1281/sao-mateus-do-sul-recebe-o-espetaculo-o-rei-louco</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>8</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:37:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>http://www.unicentro.br/uab/pnap</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>www.unicentro.br</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>www.unicentro.br/uab/pnap</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2229/esta-aberto-processo-seletivo-de-alunos-para-cursos-de-especializacao--uabmecunicentro</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>8</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:38:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cdweb/03114-315/contribuinte/main.faces</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cdweb/03114-315/contribuinte/main.faces</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2856/sexta-feira-10-e-ultimo-dia-para-quitar-alvara-com-desconto-de-40</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>8</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:38:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasalvamvidas?__eep__=6&amp;__cft__[0]=AZUv1yiTN0cXQqiCHWWdCDlOkqCTayQqXqWfak3EnEOrs-ja0DjNJ_vg43dYxsFtDsrY4u1H38N8BU9Eb8398oLcvStUtydiAAXCvv9rvGyc1EcbqncXB5cFdLvmZollOuO-JDfirlJcf1eT9GNwV-tofICxJIi0snLv-KceOTSFXvYpH2xGFlKrD15VzjDcQoo&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>#VacinaSalvamVidas</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2660/vacinacao-38-e-39-anos-sem-comorbidades</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>8</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:38:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/vacinasamas?__eep__=6&amp;__cft__[0]=AZUv1yiTN0cXQqiCHWWdCDlOkqCTayQqXqWfak3EnEOrs-ja0DjNJ_vg43dYxsFtDsrY4u1H38N8BU9Eb8398oLcvStUtydiAAXCvv9rvGyc1EcbqncXB5cFdLvmZollOuO-JDfirlJcf1eT9GNwV-tofICxJIi0snLv-KceOTSFXvYpH2xGFlKrD15VzjDcQoo&amp;__tn__=*NK*F</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>#VacinaSamas</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2660/vacinacao-38-e-39-anos-sem-comorbidades</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>8</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:38:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qal3SziSw7w&amp;fbclid=IwAR2e7puywsYupMafVyGRUm2AYQreY50RFi1e5SBswIVMU4WlamBpwDP9GaU</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qal3SziSw7w</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1216/assista-ao-vivo-a-transmissao-da-final-do-bom-de-bola--colegio-sao-mateus-x-colegio-carolina-lupion</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>8</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:38:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://goo.gl/forms/KLacB7O25Eh7zRRv1</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>goo.gl</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>https://goo.gl/forms/KLacB7O25Eh7zRRv1</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1218/sao-mateus-do-sul-tera-capacitacao-para-combate-as-drogas</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>8</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>2026-08-10 19:38:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/prefeiturasms/</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/prefeiturasms</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1183/audiencia-publica-demonstracao-e-avaliacao-do-cumprimento-das-metas-fiscais-relativas-ao-3-quadrimestre-orcamentario</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>8</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:17:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>http://www.portaldoempreendedor.gov.br/</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>www.portaldoempreendedor.gov.br</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>www.portaldoempreendedor.gov.br</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1532/meis-omissos-tem-ate-o-fim-do-mes-para-regularizar-situacao-ou-cnpj-sera-cancelado</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>8</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/story.php?story_fbid=1418170671576475&amp;id=467170173343201</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>m.facebook.com</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>https://m.facebook.com/story.php?story_fbid=1418170671576475&amp;id=467170173343201</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1441/projeto-xisto-agricola-esteve-na-pauta-de-audiencia-com-o-governador-beto-richa</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>8</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>http://www.eprotocolo.pr.gov.br/consultapublica</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>www.eprotocolo.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>www.eprotocolo.pr.gov.br/consultapublica</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1422/luiz-adyr-tem-audiencia-com-secretario-de-seguranca-publica-do-estado</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>8</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:20:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://e-gov.betha.com.br/cidadaoweb3/03014-010/rel_guiaiptu.faces</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>e-gov.betha.com.br</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>“Serviços Online”</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1607/contribuintes-podem-retirar-carne-do-iptu-2016-na-rodoviaria</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>8</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>2026-08-10 23:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://covid19.ibge.gov.br/</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>covid19.ibge.gov.br</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>https://covid19.ibge.gov.br/</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2503/agencia-do-ibge-em-sao-mateus-do-sul-inicia-pesquisa-nacional-por-amostra-de-domicilios-atraves-de-contato-telefonico/</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>8</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>2026-08-11 23:23:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>http://Decreto Municipal nº 919/202</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Decreto Municipal nº 919</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>http://Decreto Municipal nº 919/202</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2498/novas-normas-de-enfrentamento-a-pandemia-e-prevencao-a-transmissao-comunitaria-do-novo-coronavirus-em-sao-mateus-do-sul/</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>8</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>2026-08-11 23:23:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>http://www.sigo.pr.gov.br/cidadao/394</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>www.sigo.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>http://www.sigo.pr.gov.br/cidadao/394</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1257/ouvidoria-sus-a-voz-do-cidadao/</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>8</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2026-08-11 23:24:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/boletimepidemiol%C3%B3gicodoscasosdecovid19?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDj0titoIOxZp-kaxpmypvyzRMVmRYBVmkmXJk4V9Wigw-hJUcxkPVGgKg9qOTdbhsKad52zsGE6ymtd1eZyF_vDKLjXNJE7nDes7uhNjMZ0n1v6tWqLAflTuOrlNOPeB0cJxTwjGmc11W9-1zPBYp7NMo3Ng9PD6aKkBc1LrDoZktsw5LUYSgPE1v_3k6GPN6Rb1Iyztm9jtg68XJ8G43RVW4ZU_yVhzw_as6HX6X7POSKF69yI9IP3R0_4gZYMl1L0ljbTfa91iZNU7x1rK9NycCKU671y5sNTDsDq6tEMVMvEMKMSASt_y3MnIHWkpxOD2Avo9a7aSBMBWG52h7KkNhooagXRMKGyMcj&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>#BoletimEpidemiológicoDosCasosDeCovid19</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2514/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>8</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>2026-08-12 01:04:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/prefsamas?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDj0titoIOxZp-kaxpmypvyzRMVmRYBVmkmXJk4V9Wigw-hJUcxkPVGgKg9qOTdbhsKad52zsGE6ymtd1eZyF_vDKLjXNJE7nDes7uhNjMZ0n1v6tWqLAflTuOrlNOPeB0cJxTwjGmc11W9-1zPBYp7NMo3Ng9PD6aKkBc1LrDoZktsw5LUYSgPE1v_3k6GPN6Rb1Iyztm9jtg68XJ8G43RVW4ZU_yVhzw_as6HX6X7POSKF69yI9IP3R0_4gZYMl1L0ljbTfa91iZNU7x1rK9NycCKU671y5sNTDsDq6tEMVMvEMKMSASt_y3MnIHWkpxOD2Avo9a7aSBMBWG52h7KkNhooagXRMKGyMcj&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>#PrefSamas</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2514/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>8</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>2026-08-12 01:04:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/informeinstitucional?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDj0titoIOxZp-kaxpmypvyzRMVmRYBVmkmXJk4V9Wigw-hJUcxkPVGgKg9qOTdbhsKad52zsGE6ymtd1eZyF_vDKLjXNJE7nDes7uhNjMZ0n1v6tWqLAflTuOrlNOPeB0cJxTwjGmc11W9-1zPBYp7NMo3Ng9PD6aKkBc1LrDoZktsw5LUYSgPE1v_3k6GPN6Rb1Iyztm9jtg68XJ8G43RVW4ZU_yVhzw_as6HX6X7POSKF69yI9IP3R0_4gZYMl1L0ljbTfa91iZNU7x1rK9NycCKU671y5sNTDsDq6tEMVMvEMKMSASt_y3MnIHWkpxOD2Avo9a7aSBMBWG52h7KkNhooagXRMKGyMcj&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>#InformeInstitucional</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2514/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>8</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>2026-08-12 01:04:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/todoscontracovid19?__eep__=6&amp;source=feed_text&amp;epa=HASHTAG&amp;__xts__%5B0%5D=68.ARDj0titoIOxZp-kaxpmypvyzRMVmRYBVmkmXJk4V9Wigw-hJUcxkPVGgKg9qOTdbhsKad52zsGE6ymtd1eZyF_vDKLjXNJE7nDes7uhNjMZ0n1v6tWqLAflTuOrlNOPeB0cJxTwjGmc11W9-1zPBYp7NMo3Ng9PD6aKkBc1LrDoZktsw5LUYSgPE1v_3k6GPN6Rb1Iyztm9jtg68XJ8G43RVW4ZU_yVhzw_as6HX6X7POSKF69yI9IP3R0_4gZYMl1L0ljbTfa91iZNU7x1rK9NycCKU671y5sNTDsDq6tEMVMvEMKMSASt_y3MnIHWkpxOD2Avo9a7aSBMBWG52h7KkNhooagXRMKGyMcj&amp;__tn__=%2ANK-R</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>#TodosContraCovid19</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2514/boletim-epidemiologico-dos-casos-de-covid-19-em-sao-mateus-do-sul</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>8</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>2026-08-12 01:04:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>http://www.portalaprendebrasil.com.br/</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>www.portalaprendebrasil.com.br</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>www.portalaprendebrasil.com.br</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1543/ledur-visita-estande-da-editora-positivo-na-xix-marcha-a-brasilia</t>
+        </is>
+      </c>
+      <c r="F480" t="n">
+        <v>9</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>2026-08-12 01:06:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>http://www.sescpr.com.br/ddd</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>www.sescpr.com.br</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>www.sescpr.com.br/ddd</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1125/acontece-nessa-quarta-feira-29-mais-uma-edicao-do-dia-do-desafio</t>
+        </is>
+      </c>
+      <c r="F481" t="n">
+        <v>9</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>2026-08-12 03:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>http://www.diadodesafio.org.br</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>www.diadodesafio.org.br</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>www.diadodesafio.org.br</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1125/acontece-nessa-quarta-feira-29-mais-uma-edicao-do-dia-do-desafio</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>9</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>2026-08-12 03:22:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>http://pns.agenciasecreta.com.br/lt.php?c=1194&amp;m=1525&amp;nl=23&amp;s=c6e6c1ed18ea87212ea02112b5fe7306&amp;lid=6507&amp;l=-http--paineis.cgu.gov.br/index.htm</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>pns.agenciasecreta.com.br</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>http://paineis.cgu.gov.br/index.htm</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1474/luiz-adyr-e-secretarios-municipais-participam-do-encontro-municipio-transparente-promovido-pela-cgu</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>9</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>2026-08-12 03:22:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/saomateusdosul/inventario_externos.xlsx
+++ b/resultados/saomateusdosul/inventario_externos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G483"/>
+  <dimension ref="A1:G491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17271,6 +17271,286 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCxLc-Mxw-OR6XdURRAmXsfQ</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>www.youtube.com</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCxLc-Mxw-OR6XdURRAmXsfQ</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2502/prefeitura-municipal-realizara-audiencia-publica-online-para-a-prestacao-de-contas-quadrimestral</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>9</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://auxilio.caixa.gov.br/</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>auxilio.caixa.gov.br</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>https://auxilio.caixa.gov.br/#/inicio</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2488/prefeitura-municipal-fara-forca-tarefa-para-auxiliar-trabalhadores-informais-a-solicitarem-o-auxilio-emergencial</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>9</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:13:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/prefeiturasms/videos/641135126352270/</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/prefeiturasms/videos/641135126352270/</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1114/governador-ratinho-junior-assina-homologacao-para-a-revitalizacao-da-rua-ulisses-faria/</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>9</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1QYgkvbLEZuEE-xFuO1Q41SldVS1osuJo/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>drive.google.com</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/file/d/1QYgkvbLEZuEE-xFuO1Q41SldVS1osuJo/view?usp=sharing</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1114/governador-ratinho-junior-assina-homologacao-para-a-revitalizacao-da-rua-ulisses-faria/</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>9</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://www.objetivas.com.br</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>www.objetivas.com.br</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>https://www.objetivas.com.br</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1153/prefeitura-municipal-lanca-edital-para-a-realizacao-do-concurso-publico/</t>
+        </is>
+      </c>
+      <c r="F488" t="n">
+        <v>9</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>http://wordpress-196161-626839.cloudwaysapps.com/wp-content/uploads/2019/04/edital-concurso-publico.pdf</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>wordpress-196161-626839.cloudwaysapps.com</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Edital Concurso Público</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/1153/prefeitura-municipal-lanca-edital-para-a-realizacao-do-concurso-publico/</t>
+        </is>
+      </c>
+      <c r="F489" t="n">
+        <v>9</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/explore/tags/saomateuscontraacovid/</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>#SaoMateusContraACOVID</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2637/vigilancia-sanitaria-intensifica-a-fiscalizacao-em-conjunto-com-a-policia-militar/</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>9</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:17:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>saomateusdosul</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/explore/tags/fiscalizacao/</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>#Fiscalizacao</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>https://www.saomateusdosul.pr.gov.br/portal/noticias/0/3/2637/vigilancia-sanitaria-intensifica-a-fiscalizacao-em-conjunto-com-a-policia-militar/</t>
+        </is>
+      </c>
+      <c r="F491" t="n">
+        <v>9</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>2026-08-21 03:17:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
